--- a/docs/personaggi-bt3.xlsx
+++ b/docs/personaggi-bt3.xlsx
@@ -80,7 +80,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -91,6 +91,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF1F3864"/>
         <bgColor rgb="FF333333"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -113,7 +118,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -160,6 +165,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -588,7 +594,36 @@
       </c>
       <c r="I2" s="12" t="inlineStr">
         <is>
-          <t>Son Goku</t>
+          <t>Son Goku (inizio)</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K2" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L2" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M2" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N2" s="7" t="inlineStr">
+        <is>
+          <t>Kamehameha (onda)</t>
+        </is>
+      </c>
+      <c r="O2" s="7" t="inlineStr">
+        <is>
+          <t>Kaio-ken Attack (impeto)</t>
+        </is>
+      </c>
+      <c r="P2" s="7" t="inlineStr">
+        <is>
+          <t>Spirit Bomb (onda)</t>
         </is>
       </c>
     </row>
@@ -634,36 +669,41 @@
       </c>
       <c r="I3" s="12" t="inlineStr">
         <is>
-          <t>Son Goku</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3</v>
-      </c>
-      <c r="L3" t="n">
-        <v>3</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
+          <t>Son Goku (metà)</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K3" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="7" t="inlineStr">
         <is>
           <t>x20 Kaio-ken Kamehameha (onda)</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" s="7" t="inlineStr">
         <is>
           <t>Meteor Combination (impeto)</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" s="7" t="inlineStr">
         <is>
           <t>Spirit Bomb (onda)</t>
+        </is>
+      </c>
+      <c r="Q3" s="7" t="inlineStr">
+        <is>
+          <t>Son Goku (metà) SSJ</t>
         </is>
       </c>
     </row>
@@ -709,34 +749,34 @@
       </c>
       <c r="I4" s="12" t="inlineStr">
         <is>
-          <t>Son Goku</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>4</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
+          <t>Son Goku (metà)</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K4" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L4" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="7" t="inlineStr">
         <is>
           <t>Super Kamehameha (onda)</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O4" s="7" t="inlineStr">
         <is>
           <t>Meteor Smash (impeto)</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P4" s="7" t="inlineStr">
         <is>
           <t>Angry Kamehameha (onda)</t>
         </is>
@@ -784,7 +824,41 @@
       </c>
       <c r="I5" s="12" t="inlineStr">
         <is>
-          <t>Son Goku</t>
+          <t>Son Goku (fine)</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K5" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>Kamehameha (onda)</t>
+        </is>
+      </c>
+      <c r="O5" s="7" t="inlineStr">
+        <is>
+          <t>Meteor Smash (impeto)</t>
+        </is>
+      </c>
+      <c r="P5" s="7" t="inlineStr">
+        <is>
+          <t>Super Spirit Bomb (onda)</t>
+        </is>
+      </c>
+      <c r="Q5" s="7" t="inlineStr">
+        <is>
+          <t>Son Goku (fine) SSJ</t>
         </is>
       </c>
     </row>
@@ -830,7 +904,41 @@
       </c>
       <c r="I6" s="12" t="inlineStr">
         <is>
-          <t>Son Goku</t>
+          <t>Son Goku (fine)</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Super Kamehameha (onda)</t>
+        </is>
+      </c>
+      <c r="O6" s="7" t="inlineStr">
+        <is>
+          <t>Super Energy Wave Volley (impeto)</t>
+        </is>
+      </c>
+      <c r="P6" s="7" t="inlineStr">
+        <is>
+          <t>Instant Kamehameha (onda)</t>
+        </is>
+      </c>
+      <c r="Q6" s="7" t="inlineStr">
+        <is>
+          <t>Son Goku (fine) SSJ2</t>
         </is>
       </c>
     </row>
@@ -876,7 +984,41 @@
       </c>
       <c r="I7" s="12" t="inlineStr">
         <is>
-          <t>Son Goku</t>
+          <t>Son Goku (fine)</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>Kamehameha (onda)</t>
+        </is>
+      </c>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t>Meteor Crash (impeto)</t>
+        </is>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>Super Kamehameha (onda)</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>Son Goku (fine) SSJ3</t>
         </is>
       </c>
     </row>
@@ -922,7 +1064,36 @@
       </c>
       <c r="I8" s="12" t="inlineStr">
         <is>
-          <t>Son Goku</t>
+          <t>Son Goku (fine)</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="inlineStr">
+        <is>
+          <t>Super Kamehameha (onda)</t>
+        </is>
+      </c>
+      <c r="O8" s="7" t="inlineStr">
+        <is>
+          <t>Super Explosive Wave (onda)</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Dragon Fist (impeto, giganti)</t>
         </is>
       </c>
     </row>
@@ -968,7 +1139,41 @@
       </c>
       <c r="I9" s="12" t="inlineStr">
         <is>
-          <t>Son Goku</t>
+          <t>Son Goku (GT)</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K9" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L9" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="7" t="inlineStr">
+        <is>
+          <t>Kamehameha (onda)</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Dragon Fist (impeto, giganti)</t>
+        </is>
+      </c>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>Spirit Bomb (onda)</t>
+        </is>
+      </c>
+      <c r="Q9" s="7" t="inlineStr">
+        <is>
+          <t>Son Goku (GT) SSJ</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1219,41 @@
       </c>
       <c r="I10" s="12" t="inlineStr">
         <is>
-          <t>Son Goku</t>
+          <t>Son Goku (GT)</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K10" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L10" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Super Kamehameha (onda)</t>
+        </is>
+      </c>
+      <c r="O10" s="7" t="inlineStr">
+        <is>
+          <t>Full Power Energy Blast Volley (impeto)</t>
+        </is>
+      </c>
+      <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>Super Explosive Wave (onda)</t>
+        </is>
+      </c>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>Son Goku (GT) SSJ3</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1299,41 @@
       </c>
       <c r="I11" s="12" t="inlineStr">
         <is>
-          <t>Son Goku</t>
+          <t>Son Goku (GT)</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="inlineStr">
+        <is>
+          <t>Super Kamehameha (onda)</t>
+        </is>
+      </c>
+      <c r="O11" s="7" t="inlineStr">
+        <is>
+          <t>Full Power Energy Blast Volley (onda)</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Dragon Fist (impeto, giganti)</t>
+        </is>
+      </c>
+      <c r="Q11" s="7" t="inlineStr">
+        <is>
+          <t>Son Goku SSJ4</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1379,36 @@
       </c>
       <c r="I12" s="12" t="inlineStr">
         <is>
-          <t>Son Goku</t>
+          <t>Son Goku (GT)</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K12" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M12" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="7" t="inlineStr">
+        <is>
+          <t>10x Kamehameha (onda)</t>
+        </is>
+      </c>
+      <c r="O12" s="7" t="inlineStr">
+        <is>
+          <t>Meteor Crash (impeto)</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Dragon Fist (impeto, giganti)</t>
         </is>
       </c>
     </row>
@@ -1152,36 +1454,41 @@
       </c>
       <c r="I13" s="12" t="inlineStr">
         <is>
-          <t>Son Goku</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>3</v>
-      </c>
-      <c r="K13" t="n">
+          <t>Son Goku (bambino)</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="L13" t="n">
-        <v>4</v>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
+      <c r="L13" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="inlineStr">
         <is>
           <t>Kamehameha (onda)</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O13" s="7" t="inlineStr">
         <is>
           <t>Counterattack! (impeto)</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P13" s="7" t="inlineStr">
         <is>
           <t>Penetrate! (impeto, giganti)</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Son Goku (bambino) Oozaru</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1534,36 @@
       </c>
       <c r="I14" s="12" t="inlineStr">
         <is>
-          <t>Son Goku</t>
+          <t>Son Goku (bambino)</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>5</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5</v>
+      </c>
+      <c r="L14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
+      <c r="N14" s="7" t="inlineStr">
+        <is>
+          <t>Chou Makouhou (onda)</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Gigant Rock Throw (onda)</t>
+        </is>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>Chou Makouhou Barrage (onda)</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1609,36 @@
       </c>
       <c r="I15" s="12" t="inlineStr">
         <is>
-          <t>Son Gohan</t>
+          <t>Son Gohan (bambino)</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="inlineStr">
+        <is>
+          <t>Masenko (onda)</t>
+        </is>
+      </c>
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t>Gekiretsu Madan (onda)</t>
+        </is>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>Bakuretsu Ranma (impeto)</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1684,41 @@
       </c>
       <c r="I16" s="12" t="inlineStr">
         <is>
-          <t>Son Gohan</t>
+          <t>Son Gohan (ragazzo)</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L16" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="7" t="inlineStr">
+        <is>
+          <t>Super Masenko (onda)</t>
+        </is>
+      </c>
+      <c r="O16" s="7" t="inlineStr">
+        <is>
+          <t>Gekiretsu Madan (onda)</t>
+        </is>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>Super Kamehameha (onda)</t>
+        </is>
+      </c>
+      <c r="Q16" s="7" t="inlineStr">
+        <is>
+          <t>Son Gohan (ragazzo) SSJ</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1764,41 @@
       </c>
       <c r="I17" s="12" t="inlineStr">
         <is>
-          <t>Son Gohan</t>
+          <t>Son Gohan (ragazzo)</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L17" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="inlineStr">
+        <is>
+          <t>Super Masenko (onda)</t>
+        </is>
+      </c>
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t>Chou Maretsugeki (impeto)</t>
+        </is>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>Super Kamehameha (onda)</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>Son Gohan (ragazzo) SSJ2</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1844,36 @@
       </c>
       <c r="I18" s="12" t="inlineStr">
         <is>
-          <t>Son Gohan</t>
+          <t>Son Gohan (ragazzo)</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K18" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L18" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M18" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="7" t="inlineStr">
+        <is>
+          <t>Super Kamehameha (onda)</t>
+        </is>
+      </c>
+      <c r="O18" s="7" t="inlineStr">
+        <is>
+          <t>Gekiretsu Madan (onda)</t>
+        </is>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>Father-Son Kamehameha (onda)</t>
         </is>
       </c>
     </row>
@@ -1460,6 +1922,40 @@
           <t>Son Gohan</t>
         </is>
       </c>
+      <c r="J19" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K19" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L19" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M19" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="inlineStr">
+        <is>
+          <t>Explosive Madan (onda)</t>
+        </is>
+      </c>
+      <c r="O19" s="7" t="inlineStr">
+        <is>
+          <t>Full Power Energy Blast Volley (onda)</t>
+        </is>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>Super Kamehameha (onda)</t>
+        </is>
+      </c>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>Son Gohan SSJ</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="8">
       <c r="A20" s="12" t="inlineStr">
@@ -1506,6 +2002,40 @@
           <t>Son Gohan</t>
         </is>
       </c>
+      <c r="J20" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K20" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L20" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M20" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="7" t="inlineStr">
+        <is>
+          <t>Explosive Madan (onda)</t>
+        </is>
+      </c>
+      <c r="O20" s="7" t="inlineStr">
+        <is>
+          <t>Full Power Energy Blast Volley (onda)</t>
+        </is>
+      </c>
+      <c r="P20" s="7" t="inlineStr">
+        <is>
+          <t>Bros. Kamehameha (onda)</t>
+        </is>
+      </c>
+      <c r="Q20" s="7" t="inlineStr">
+        <is>
+          <t>Son Gohan SSJ2</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="8">
       <c r="A21" s="12" t="inlineStr">
@@ -1552,6 +2082,35 @@
           <t>Son Gohan</t>
         </is>
       </c>
+      <c r="J21" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K21" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L21" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="inlineStr">
+        <is>
+          <t>Super Explosive Madan (onda)</t>
+        </is>
+      </c>
+      <c r="O21" s="7" t="inlineStr">
+        <is>
+          <t>Full Power Energy Barrage Wave (onda)</t>
+        </is>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>Super Kamehameha (onda)</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="8">
       <c r="A22" s="12" t="inlineStr">
@@ -1595,7 +2154,36 @@
       </c>
       <c r="I22" s="12" t="inlineStr">
         <is>
-          <t>Son Gohan</t>
+          <t>Great Saiyaman</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K22" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L22" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M22" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="inlineStr">
+        <is>
+          <t>Super Explosive Wave (onda)</t>
+        </is>
+      </c>
+      <c r="O22" s="7" t="inlineStr">
+        <is>
+          <t>Justice Slash (impeto)</t>
+        </is>
+      </c>
+      <c r="P22" s="7" t="inlineStr">
+        <is>
+          <t>Justice Judgment (impeto)</t>
         </is>
       </c>
     </row>
@@ -1641,7 +2229,36 @@
       </c>
       <c r="I23" s="12" t="inlineStr">
         <is>
-          <t>Son Gohan</t>
+          <t>Son Gohan (Ultimate)</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K23" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L23" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="inlineStr">
+        <is>
+          <t>Super Kamehameha (onda)</t>
+        </is>
+      </c>
+      <c r="O23" s="7" t="inlineStr">
+        <is>
+          <t>Super Explosive Wave (onda)</t>
+        </is>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>Burst Rush (impeto)</t>
         </is>
       </c>
     </row>
@@ -1690,6 +2307,40 @@
           <t>Son Gohan (futuro)</t>
         </is>
       </c>
+      <c r="J24" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K24" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L24" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M24" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="7" t="inlineStr">
+        <is>
+          <t>Masenko (onda)</t>
+        </is>
+      </c>
+      <c r="O24" s="7" t="inlineStr">
+        <is>
+          <t>Super Explosive Wave (onda)</t>
+        </is>
+      </c>
+      <c r="P24" s="7" t="inlineStr">
+        <is>
+          <t>Super Kamehameha (onda)</t>
+        </is>
+      </c>
+      <c r="Q24" s="7" t="inlineStr">
+        <is>
+          <t>Son Gohan (futuro) SSJ</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="8">
       <c r="A25" s="12" t="inlineStr">
@@ -1736,6 +2387,35 @@
           <t>Son Gohan (futuro)</t>
         </is>
       </c>
+      <c r="J25" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K25" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L25" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M25" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="7" t="inlineStr">
+        <is>
+          <t>Gekiretsu Madan (onda)</t>
+        </is>
+      </c>
+      <c r="O25" s="7" t="inlineStr">
+        <is>
+          <t>Special Beam Cannon (onda)</t>
+        </is>
+      </c>
+      <c r="P25" s="7" t="inlineStr">
+        <is>
+          <t>Gekiretsu Ranbu (impeto)</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="8">
       <c r="A26" s="12" t="inlineStr">
@@ -1782,6 +2462,40 @@
           <t>Son Goten</t>
         </is>
       </c>
+      <c r="J26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2</v>
+      </c>
+      <c r="L26" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M26" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="7" t="inlineStr">
+        <is>
+          <t>Full Power Energy Blast Volley (onda)</t>
+        </is>
+      </c>
+      <c r="O26" s="7" t="inlineStr">
+        <is>
+          <t>Assault! (impeto)</t>
+        </is>
+      </c>
+      <c r="P26" s="7" t="inlineStr">
+        <is>
+          <t>Super Kamehameha (onda)</t>
+        </is>
+      </c>
+      <c r="Q26" s="7" t="inlineStr">
+        <is>
+          <t>Son Goten SSJ</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="8">
       <c r="A27" s="12" t="inlineStr">
@@ -1828,31 +2542,31 @@
           <t>Son Goten</t>
         </is>
       </c>
-      <c r="J27" t="n">
-        <v>3</v>
-      </c>
-      <c r="K27" t="n">
+      <c r="J27" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K27" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="L27" t="n">
-        <v>4</v>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
+      <c r="L27" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M27" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="inlineStr">
         <is>
           <t>Kamehameha (onda)</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="O27" s="7" t="inlineStr">
         <is>
           <t>Assault! (impeto)</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="P27" s="7" t="inlineStr">
         <is>
           <t>Bros. Kamehameha (onda)</t>
         </is>
@@ -1900,7 +2614,41 @@
       </c>
       <c r="I28" s="12" t="inlineStr">
         <is>
-          <t>Vegeta</t>
+          <t>Vegeta (scouter)</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K28" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L28" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M28" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="7" t="inlineStr">
+        <is>
+          <t>Galick Gun (onda)</t>
+        </is>
+      </c>
+      <c r="O28" s="7" t="inlineStr">
+        <is>
+          <t>Final Galick Cannon (impeto)</t>
+        </is>
+      </c>
+      <c r="P28" s="7" t="inlineStr">
+        <is>
+          <t>Dirty Fireworks (impeto)</t>
+        </is>
+      </c>
+      <c r="Q28" s="7" t="inlineStr">
+        <is>
+          <t>Vegeta (scouter) Oozaru</t>
         </is>
       </c>
     </row>
@@ -1946,34 +2694,34 @@
       </c>
       <c r="I29" s="12" t="inlineStr">
         <is>
-          <t>Vegeta</t>
-        </is>
-      </c>
-      <c r="J29" t="n">
+          <t>Vegeta (scouter)</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="K29" t="n">
+      <c r="K29" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="L29" t="n">
+      <c r="L29" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M29" s="7" t="inlineStr">
         <is>
           <t>sì</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N29" s="7" t="inlineStr">
         <is>
           <t>Chou Makouhou (onda)</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="O29" s="7" t="inlineStr">
         <is>
           <t>Chou Makouhou Barrage (onda)</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="P29" s="7" t="inlineStr">
         <is>
           <t>Super Galick Gun (onda)</t>
         </is>
@@ -2024,6 +2772,40 @@
           <t>Vegeta</t>
         </is>
       </c>
+      <c r="J30" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K30" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L30" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M30" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="7" t="inlineStr">
+        <is>
+          <t>Galick Gun (onda)</t>
+        </is>
+      </c>
+      <c r="O30" s="7" t="inlineStr">
+        <is>
+          <t>Super Energy Wave Volley (onda)</t>
+        </is>
+      </c>
+      <c r="P30" s="7" t="inlineStr">
+        <is>
+          <t>Super Explosive Wave (onda)</t>
+        </is>
+      </c>
+      <c r="Q30" s="7" t="inlineStr">
+        <is>
+          <t>Vegeta SSJ</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="8">
       <c r="A31" s="12" t="inlineStr">
@@ -2070,6 +2852,40 @@
           <t>Vegeta</t>
         </is>
       </c>
+      <c r="J31" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K31" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L31" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M31" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="7" t="inlineStr">
+        <is>
+          <t>Maximum Flasher (onda)</t>
+        </is>
+      </c>
+      <c r="O31" s="7" t="inlineStr">
+        <is>
+          <t>Amazing Impact (impeto)</t>
+        </is>
+      </c>
+      <c r="P31" s="7" t="inlineStr">
+        <is>
+          <t>Big Bang Attack (onda)</t>
+        </is>
+      </c>
+      <c r="Q31" s="7" t="inlineStr">
+        <is>
+          <t>Super Vegeta</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="8">
       <c r="A32" s="12" t="inlineStr">
@@ -2116,6 +2932,35 @@
           <t>Vegeta</t>
         </is>
       </c>
+      <c r="J32" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K32" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L32" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M32" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="7" t="inlineStr">
+        <is>
+          <t>Big Bang Attack (onda)</t>
+        </is>
+      </c>
+      <c r="O32" s="7" t="inlineStr">
+        <is>
+          <t>Spirit Breaking Cannon (impeto)</t>
+        </is>
+      </c>
+      <c r="P32" s="7" t="inlineStr">
+        <is>
+          <t>Final Flash (onda)</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="8">
       <c r="A33" s="12" t="inlineStr">
@@ -2159,7 +3004,41 @@
       </c>
       <c r="I33" s="12" t="inlineStr">
         <is>
-          <t>Vegeta</t>
+          <t>Vegeta (seconda forma)</t>
+        </is>
+      </c>
+      <c r="J33" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K33" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L33" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M33" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="7" t="inlineStr">
+        <is>
+          <t>Galick Gun (onda)</t>
+        </is>
+      </c>
+      <c r="O33" s="7" t="inlineStr">
+        <is>
+          <t>Super Energy Wave Volley (onda)</t>
+        </is>
+      </c>
+      <c r="P33" s="7" t="inlineStr">
+        <is>
+          <t>Big Bang Attack (onda)</t>
+        </is>
+      </c>
+      <c r="Q33" s="7" t="inlineStr">
+        <is>
+          <t>Vegeta (seconda forma) SSJ</t>
         </is>
       </c>
     </row>
@@ -2205,7 +3084,41 @@
       </c>
       <c r="I34" s="12" t="inlineStr">
         <is>
-          <t>Vegeta</t>
+          <t>Vegeta (seconda forma)</t>
+        </is>
+      </c>
+      <c r="J34" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K34" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L34" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M34" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="7" t="inlineStr">
+        <is>
+          <t>Final Flash (onda)</t>
+        </is>
+      </c>
+      <c r="O34" s="7" t="inlineStr">
+        <is>
+          <t>Super Energy Wave Volley (onda)</t>
+        </is>
+      </c>
+      <c r="P34" s="7" t="inlineStr">
+        <is>
+          <t>Super Explosive Wave (onda)</t>
+        </is>
+      </c>
+      <c r="Q34" s="7" t="inlineStr">
+        <is>
+          <t>Vegeta (seconda forma) SSJ2</t>
         </is>
       </c>
     </row>
@@ -2251,7 +3164,36 @@
       </c>
       <c r="I35" s="12" t="inlineStr">
         <is>
-          <t>Vegeta</t>
+          <t>Vegeta (seconda forma)</t>
+        </is>
+      </c>
+      <c r="J35" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K35" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L35" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M35" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="7" t="inlineStr">
+        <is>
+          <t>Big Bang Attack (onda)</t>
+        </is>
+      </c>
+      <c r="O35" s="7" t="inlineStr">
+        <is>
+          <t>Super Energy Wave Volley (onda)</t>
+        </is>
+      </c>
+      <c r="P35" s="7" t="inlineStr">
+        <is>
+          <t>Final Flash (onda)</t>
         </is>
       </c>
     </row>
@@ -2297,7 +3239,36 @@
       </c>
       <c r="I36" s="12" t="inlineStr">
         <is>
-          <t>Vegeta</t>
+          <t>Majin Vegeta</t>
+        </is>
+      </c>
+      <c r="J36" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K36" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L36" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M36" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="7" t="inlineStr">
+        <is>
+          <t>Final Impact (onda)</t>
+        </is>
+      </c>
+      <c r="O36" s="7" t="inlineStr">
+        <is>
+          <t>Big Bang Attack (onda)</t>
+        </is>
+      </c>
+      <c r="P36" s="7" t="inlineStr">
+        <is>
+          <t>Final Explosion (onda)</t>
         </is>
       </c>
     </row>
@@ -2343,7 +3314,36 @@
       </c>
       <c r="I37" s="12" t="inlineStr">
         <is>
-          <t>Vegeta</t>
+          <t>Vegeta SSJ4</t>
+        </is>
+      </c>
+      <c r="J37" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K37" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L37" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M37" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="7" t="inlineStr">
+        <is>
+          <t>Final Flash (onda)</t>
+        </is>
+      </c>
+      <c r="O37" s="7" t="inlineStr">
+        <is>
+          <t>Spirit Breaking Cannon (impeto)</t>
+        </is>
+      </c>
+      <c r="P37" s="7" t="inlineStr">
+        <is>
+          <t>Final Shine Attack (onda)</t>
         </is>
       </c>
     </row>
@@ -2389,7 +3389,41 @@
       </c>
       <c r="I38" s="12" t="inlineStr">
         <is>
-          <t>Trunks</t>
+          <t>Trunks (spada)</t>
+        </is>
+      </c>
+      <c r="J38" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K38" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L38" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M38" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="7" t="inlineStr">
+        <is>
+          <t>Finish Buster (onda)</t>
+        </is>
+      </c>
+      <c r="O38" s="7" t="inlineStr">
+        <is>
+          <t>Burning Storm (onda)</t>
+        </is>
+      </c>
+      <c r="P38" s="7" t="inlineStr">
+        <is>
+          <t>Lightning Sword Slash (onda)</t>
+        </is>
+      </c>
+      <c r="Q38" s="7" t="inlineStr">
+        <is>
+          <t>Trunks (spada) SSJ</t>
         </is>
       </c>
     </row>
@@ -2435,7 +3469,36 @@
       </c>
       <c r="I39" s="12" t="inlineStr">
         <is>
-          <t>Trunks</t>
+          <t>Trunks (spada)</t>
+        </is>
+      </c>
+      <c r="J39" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K39" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L39" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M39" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="7" t="inlineStr">
+        <is>
+          <t>Burning Attack (onda)</t>
+        </is>
+      </c>
+      <c r="O39" s="7" t="inlineStr">
+        <is>
+          <t>Burning Storm (onda)</t>
+        </is>
+      </c>
+      <c r="P39" s="7" t="inlineStr">
+        <is>
+          <t>Shining Sword Attack (impeto)</t>
         </is>
       </c>
     </row>
@@ -2484,6 +3547,40 @@
           <t>Trunks</t>
         </is>
       </c>
+      <c r="J40" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K40" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L40" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M40" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="7" t="inlineStr">
+        <is>
+          <t>Burning Attack (onda)</t>
+        </is>
+      </c>
+      <c r="O40" s="7" t="inlineStr">
+        <is>
+          <t>High Speed Rush (impeto)</t>
+        </is>
+      </c>
+      <c r="P40" s="7" t="inlineStr">
+        <is>
+          <t>Finish Buster (onda)</t>
+        </is>
+      </c>
+      <c r="Q40" s="7" t="inlineStr">
+        <is>
+          <t>Trunks SSJ</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="8">
       <c r="A41" s="12" t="inlineStr">
@@ -2530,6 +3627,40 @@
           <t>Trunks</t>
         </is>
       </c>
+      <c r="J41" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K41" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L41" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M41" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="7" t="inlineStr">
+        <is>
+          <t>Burning Attack (onda)</t>
+        </is>
+      </c>
+      <c r="O41" s="7" t="inlineStr">
+        <is>
+          <t>Burning Breaker (impeto)</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Heat Dome Attack (impeto, giganti)</t>
+        </is>
+      </c>
+      <c r="Q41" s="7" t="inlineStr">
+        <is>
+          <t>Super Trunks</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="8">
       <c r="A42" s="12" t="inlineStr">
@@ -2576,6 +3707,35 @@
           <t>Trunks</t>
         </is>
       </c>
+      <c r="J42" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K42" t="n">
+        <v>4</v>
+      </c>
+      <c r="L42" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M42" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="7" t="inlineStr">
+        <is>
+          <t>Finish Buster (onda)</t>
+        </is>
+      </c>
+      <c r="O42" s="7" t="inlineStr">
+        <is>
+          <t>Burning Attack (onda)</t>
+        </is>
+      </c>
+      <c r="P42" s="7" t="inlineStr">
+        <is>
+          <t>Super Explosive Wave (onda)</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="8">
       <c r="A43" s="12" t="inlineStr">
@@ -2622,6 +3782,40 @@
           <t>Trunks (bambino)</t>
         </is>
       </c>
+      <c r="J43" t="n">
+        <v>3</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2</v>
+      </c>
+      <c r="L43" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M43" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="7" t="inlineStr">
+        <is>
+          <t>Full Power Energy Wave (onda)</t>
+        </is>
+      </c>
+      <c r="O43" s="7" t="inlineStr">
+        <is>
+          <t>High Speed Rush (impeto)</t>
+        </is>
+      </c>
+      <c r="P43" s="7" t="inlineStr">
+        <is>
+          <t>Finish Buster (onda)</t>
+        </is>
+      </c>
+      <c r="Q43" s="7" t="inlineStr">
+        <is>
+          <t>Trunks (bambino) SSJ</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="8">
       <c r="A44" s="12" t="inlineStr">
@@ -2668,6 +3862,35 @@
           <t>Trunks (bambino)</t>
         </is>
       </c>
+      <c r="J44" t="n">
+        <v>3</v>
+      </c>
+      <c r="K44" t="n">
+        <v>2</v>
+      </c>
+      <c r="L44" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M44" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="7" t="inlineStr">
+        <is>
+          <t>Full Power Energy Barrage Wave (onda)</t>
+        </is>
+      </c>
+      <c r="O44" s="7" t="inlineStr">
+        <is>
+          <t>High Speed Rush (impeto)</t>
+        </is>
+      </c>
+      <c r="P44" s="7" t="inlineStr">
+        <is>
+          <t>Big Tree Cannon (onda)</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="8">
       <c r="A45" s="12" t="inlineStr">
@@ -2714,6 +3937,40 @@
           <t>Gotenks</t>
         </is>
       </c>
+      <c r="J45" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K45" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L45" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="7" t="inlineStr">
+        <is>
+          <t>Full Power Energy Wave (onda)</t>
+        </is>
+      </c>
+      <c r="O45" s="7" t="inlineStr">
+        <is>
+          <t>High Speed Rush (impeto)</t>
+        </is>
+      </c>
+      <c r="P45" s="7" t="inlineStr">
+        <is>
+          <t>Big Tree Cannon (onda)</t>
+        </is>
+      </c>
+      <c r="Q45" s="7" t="inlineStr">
+        <is>
+          <t>Gotenks SSJ</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="8">
       <c r="A46" s="12" t="inlineStr">
@@ -2760,6 +4017,40 @@
           <t>Gotenks</t>
         </is>
       </c>
+      <c r="J46" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K46" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L46" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M46" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="7" t="inlineStr">
+        <is>
+          <t>Big Tree Cannon (onda)</t>
+        </is>
+      </c>
+      <c r="O46" s="7" t="inlineStr">
+        <is>
+          <t>Galactic Donuts (onda)</t>
+        </is>
+      </c>
+      <c r="P46" s="7" t="inlineStr">
+        <is>
+          <t>Super Ghost Kamikaze Attack (onda)</t>
+        </is>
+      </c>
+      <c r="Q46" s="7" t="inlineStr">
+        <is>
+          <t>Gotenks SSJ3</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="8">
       <c r="A47" s="12" t="inlineStr">
@@ -2806,6 +4097,35 @@
           <t>Gotenks</t>
         </is>
       </c>
+      <c r="J47" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K47" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L47" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M47" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="7" t="inlineStr">
+        <is>
+          <t>Big Tree Cannon (onda)</t>
+        </is>
+      </c>
+      <c r="O47" s="7" t="inlineStr">
+        <is>
+          <t>DIE DIE Missile Barrage (onda)</t>
+        </is>
+      </c>
+      <c r="P47" s="7" t="inlineStr">
+        <is>
+          <t>Charging Ultra Buu Buu Volleyball (impeto)</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="8">
       <c r="A48" s="12" t="inlineStr">
@@ -2852,6 +4172,40 @@
           <t>Vegetto</t>
         </is>
       </c>
+      <c r="J48" t="n">
+        <v>5</v>
+      </c>
+      <c r="K48" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L48" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M48" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="7" t="inlineStr">
+        <is>
+          <t>Big Bang Attack (onda)</t>
+        </is>
+      </c>
+      <c r="O48" s="7" t="inlineStr">
+        <is>
+          <t>Scatter Finger Beam (onda)</t>
+        </is>
+      </c>
+      <c r="P48" s="7" t="inlineStr">
+        <is>
+          <t>Super Kamehameha (onda)</t>
+        </is>
+      </c>
+      <c r="Q48" s="7" t="inlineStr">
+        <is>
+          <t>Super Vegetto</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="8">
       <c r="A49" s="12" t="inlineStr">
@@ -2898,6 +4252,35 @@
           <t>Vegetto</t>
         </is>
       </c>
+      <c r="J49" t="n">
+        <v>5</v>
+      </c>
+      <c r="K49" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L49" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="7" t="inlineStr">
+        <is>
+          <t>Super Kamehameha (onda)</t>
+        </is>
+      </c>
+      <c r="O49" s="7" t="inlineStr">
+        <is>
+          <t>Beam Sword Slash (impeto)</t>
+        </is>
+      </c>
+      <c r="P49" s="7" t="inlineStr">
+        <is>
+          <t>Final Kamehameha (onda)</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="8">
       <c r="A50" s="12" t="inlineStr">
@@ -2941,7 +4324,36 @@
       </c>
       <c r="I50" s="12" t="inlineStr">
         <is>
-          <t>Gogeta</t>
+          <t>Super Gogeta</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>5</v>
+      </c>
+      <c r="K50" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L50" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M50" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="7" t="inlineStr">
+        <is>
+          <t>Big Bang Kamehameha (onda)</t>
+        </is>
+      </c>
+      <c r="O50" s="7" t="inlineStr">
+        <is>
+          <t>Super Explosive Wave (onda)</t>
+        </is>
+      </c>
+      <c r="P50" s="7" t="inlineStr">
+        <is>
+          <t>Stardust Breaker (impeto)</t>
         </is>
       </c>
     </row>
@@ -2987,34 +4399,34 @@
       </c>
       <c r="I51" s="12" t="inlineStr">
         <is>
-          <t>Gogeta</t>
-        </is>
-      </c>
-      <c r="J51" t="n">
+          <t>Gogeta SSJ4</t>
+        </is>
+      </c>
+      <c r="J51" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="K51" t="n">
-        <v>3</v>
-      </c>
-      <c r="L51" t="n">
-        <v>3</v>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
+      <c r="K51" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L51" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="7" t="inlineStr">
         <is>
           <t>Big Bang Kamehameha (onda)</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="O51" s="7" t="inlineStr">
         <is>
           <t>Ultimate Impact (impeto)</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="P51" s="7" t="inlineStr">
         <is>
           <t>100x Big Bang Kamehameha (onda)</t>
         </is>
@@ -3062,7 +4474,36 @@
       </c>
       <c r="I52" s="12" t="inlineStr">
         <is>
-          <t>Piccolo</t>
+          <t>Piccolo (inizio)</t>
+        </is>
+      </c>
+      <c r="J52" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K52" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L52" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M52" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="7" t="inlineStr">
+        <is>
+          <t>Explosive Demon Wave (onda)</t>
+        </is>
+      </c>
+      <c r="O52" s="7" t="inlineStr">
+        <is>
+          <t>Bakuretsu Mahoko (impeto)</t>
+        </is>
+      </c>
+      <c r="P52" s="7" t="inlineStr">
+        <is>
+          <t>Special Beam Cannon (onda)</t>
         </is>
       </c>
     </row>
@@ -3108,7 +4549,36 @@
       </c>
       <c r="I53" s="12" t="inlineStr">
         <is>
-          <t>Piccolo</t>
+          <t>Piccolo (fine)</t>
+        </is>
+      </c>
+      <c r="J53" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K53" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L53" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="7" t="inlineStr">
+        <is>
+          <t>Special Beam Cannon (onda)</t>
+        </is>
+      </c>
+      <c r="O53" s="7" t="inlineStr">
+        <is>
+          <t>Light Grenade (onda)</t>
+        </is>
+      </c>
+      <c r="P53" s="7" t="inlineStr">
+        <is>
+          <t>Hellzone Grenade (onda)</t>
         </is>
       </c>
     </row>
@@ -3157,6 +4627,35 @@
           <t>Krilin</t>
         </is>
       </c>
+      <c r="J54" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K54" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L54" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M54" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="7" t="inlineStr">
+        <is>
+          <t>Kamehameha (onda)</t>
+        </is>
+      </c>
+      <c r="O54" s="7" t="inlineStr">
+        <is>
+          <t>Expanding Energy Wave (onda)</t>
+        </is>
+      </c>
+      <c r="P54" s="7" t="inlineStr">
+        <is>
+          <t>Destructo Disc (onda)</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="15" customHeight="1" s="8">
       <c r="A55" s="12" t="inlineStr">
@@ -3203,6 +4702,35 @@
           <t>Yamcha</t>
         </is>
       </c>
+      <c r="J55" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K55" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L55" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="7" t="inlineStr">
+        <is>
+          <t>Kamehameha (onda)</t>
+        </is>
+      </c>
+      <c r="O55" s="7" t="inlineStr">
+        <is>
+          <t>Wolf Fang Fist (impeto)</t>
+        </is>
+      </c>
+      <c r="P55" s="7" t="inlineStr">
+        <is>
+          <t>Soukidan (onda)</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="15" customHeight="1" s="8">
       <c r="A56" s="12" t="inlineStr">
@@ -3249,6 +4777,35 @@
           <t>Tenshinhan</t>
         </is>
       </c>
+      <c r="J56" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K56" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L56" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M56" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="7" t="inlineStr">
+        <is>
+          <t>Dodon Ray (onda)</t>
+        </is>
+      </c>
+      <c r="O56" s="7" t="inlineStr">
+        <is>
+          <t>Ki Blast Cannon (onda)</t>
+        </is>
+      </c>
+      <c r="P56" s="7" t="inlineStr">
+        <is>
+          <t>Neo Tri-Beam (onda)</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="15" customHeight="1" s="8">
       <c r="A57" s="12" t="inlineStr">
@@ -3295,6 +4852,35 @@
           <t>Jiaozi</t>
         </is>
       </c>
+      <c r="J57" t="n">
+        <v>3</v>
+      </c>
+      <c r="K57" t="n">
+        <v>2</v>
+      </c>
+      <c r="L57" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Dodon Ray (onda)</t>
+        </is>
+      </c>
+      <c r="O57" s="7" t="inlineStr">
+        <is>
+          <t>Psychic Rock Throw (impeto)</t>
+        </is>
+      </c>
+      <c r="P57" s="7" t="inlineStr">
+        <is>
+          <t>Farewell, Mr. Tien (onda)</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="15" customHeight="1" s="8">
       <c r="A58" s="12" t="inlineStr">
@@ -3341,6 +4927,35 @@
           <t>Yajirobe</t>
         </is>
       </c>
+      <c r="J58" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K58" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L58" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M58" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="7" t="inlineStr">
+        <is>
+          <t>Ka-Blam Slicer (onda)</t>
+        </is>
+      </c>
+      <c r="O58" s="7" t="inlineStr">
+        <is>
+          <t>Flash and Kill (impeto)</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Miracle Ka-Blam Slash (impeto, giganti)</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="15" customHeight="1" s="8">
       <c r="A59" s="12" t="inlineStr">
@@ -3387,6 +5002,40 @@
           <t>Muten Roshi</t>
         </is>
       </c>
+      <c r="J59" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K59" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L59" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="7" t="inlineStr">
+        <is>
+          <t>The Original Kamehameha (onda)</t>
+        </is>
+      </c>
+      <c r="O59" s="7" t="inlineStr">
+        <is>
+          <t>High Speed Rush (impeto)</t>
+        </is>
+      </c>
+      <c r="P59" s="7" t="inlineStr">
+        <is>
+          <t>Mankoku Kyoutenshou (onda)</t>
+        </is>
+      </c>
+      <c r="Q59" s="7" t="inlineStr">
+        <is>
+          <t>Muten Roshi (massima potenza)</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="15" customHeight="1" s="8">
       <c r="A60" s="12" t="inlineStr">
@@ -3433,6 +5082,35 @@
           <t>Muten Roshi</t>
         </is>
       </c>
+      <c r="J60" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K60" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L60" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M60" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="7" t="inlineStr">
+        <is>
+          <t>The Original Kamehameha (onda)</t>
+        </is>
+      </c>
+      <c r="O60" s="7" t="inlineStr">
+        <is>
+          <t>Turtle School Ultimate Fist (impeto)</t>
+        </is>
+      </c>
+      <c r="P60" s="7" t="inlineStr">
+        <is>
+          <t>MAX Power Kamehameha (onda)</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="15" customHeight="1" s="8">
       <c r="A61" s="12" t="inlineStr">
@@ -3479,6 +5157,40 @@
           <t>Videl</t>
         </is>
       </c>
+      <c r="J61" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K61" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L61" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="7" t="inlineStr">
+        <is>
+          <t>High Speed Rush (impeto)</t>
+        </is>
+      </c>
+      <c r="O61" s="7" t="inlineStr">
+        <is>
+          <t>Desperado Rush (impeto)</t>
+        </is>
+      </c>
+      <c r="P61" s="7" t="inlineStr">
+        <is>
+          <t>Videl Rush (impeto)</t>
+        </is>
+      </c>
+      <c r="Q61" s="7" t="inlineStr">
+        <is>
+          <t>Great Saiyaman 2-go</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="15" customHeight="1" s="8">
       <c r="A62" s="12" t="inlineStr">
@@ -3525,6 +5237,35 @@
           <t>Videl</t>
         </is>
       </c>
+      <c r="J62" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K62" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L62" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M62" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="7" t="inlineStr">
+        <is>
+          <t>Justice Countdown (impeto)</t>
+        </is>
+      </c>
+      <c r="O62" s="7" t="inlineStr">
+        <is>
+          <t>Justice Rush 2 (impeto)</t>
+        </is>
+      </c>
+      <c r="P62" s="7" t="inlineStr">
+        <is>
+          <t>Justice Judgment (impeto)</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="15" customHeight="1" s="8">
       <c r="A63" s="12" t="inlineStr">
@@ -3571,31 +5312,31 @@
           <t>Mr. Satan</t>
         </is>
       </c>
-      <c r="J63" t="n">
-        <v>4</v>
-      </c>
-      <c r="K63" t="n">
-        <v>3</v>
-      </c>
-      <c r="L63" t="n">
-        <v>3</v>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
+      <c r="J63" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K63" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L63" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M63" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="7" t="inlineStr">
         <is>
           <t>Dynamic Mess Em Up Punch (impeto)</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
+      <c r="O63" s="7" t="inlineStr">
         <is>
           <t>Present Bomb (onda)</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="P63" s="7" t="inlineStr">
         <is>
           <t>Mister Buu Arrives! (impeto)</t>
         </is>
@@ -3646,6 +5387,40 @@
           <t>Kaioshin</t>
         </is>
       </c>
+      <c r="J64" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K64" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L64" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M64" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="7" t="inlineStr">
+        <is>
+          <t>Energy's Last (onda)</t>
+        </is>
+      </c>
+      <c r="O64" s="7" t="inlineStr">
+        <is>
+          <t>Crazy Rush (impeto)</t>
+        </is>
+      </c>
+      <c r="P64" s="7" t="inlineStr">
+        <is>
+          <t>Gekiretsu Shin'ou'hou (onda)</t>
+        </is>
+      </c>
+      <c r="Q64" s="7" t="inlineStr">
+        <is>
+          <t>Kibitoshin</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="15" customHeight="1" s="8">
       <c r="A65" s="12" t="inlineStr">
@@ -3689,7 +5464,36 @@
       </c>
       <c r="I65" s="12" t="inlineStr">
         <is>
-          <t>Kibitoshin</t>
+          <t>Kaioshin</t>
+        </is>
+      </c>
+      <c r="J65" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K65" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L65" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M65" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="7" t="inlineStr">
+        <is>
+          <t>Full Power Energy Wave (onda)</t>
+        </is>
+      </c>
+      <c r="O65" s="7" t="inlineStr">
+        <is>
+          <t>Crazy Combination (impeto)</t>
+        </is>
+      </c>
+      <c r="P65" s="7" t="inlineStr">
+        <is>
+          <t>Shin Gekiretsu Shin'ou'hou (onda)</t>
         </is>
       </c>
     </row>
@@ -3738,6 +5542,40 @@
           <t>Uub</t>
         </is>
       </c>
+      <c r="J66" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K66" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L66" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M66" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="7" t="inlineStr">
+        <is>
+          <t>Super Kamehameha (onda)</t>
+        </is>
+      </c>
+      <c r="O66" s="7" t="inlineStr">
+        <is>
+          <t>Blazing Barrage Palm (impeto)</t>
+        </is>
+      </c>
+      <c r="P66" s="7" t="inlineStr">
+        <is>
+          <t>Super Explosive Wave (onda)</t>
+        </is>
+      </c>
+      <c r="Q66" s="7" t="inlineStr">
+        <is>
+          <t>Super Uub</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="15" customHeight="1" s="8">
       <c r="A67" s="12" t="inlineStr">
@@ -3784,6 +5622,35 @@
           <t>Uub</t>
         </is>
       </c>
+      <c r="J67" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K67" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L67" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M67" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="7" t="inlineStr">
+        <is>
+          <t>Super Energy Wave Volley (onda)</t>
+        </is>
+      </c>
+      <c r="O67" s="7" t="inlineStr">
+        <is>
+          <t>Chocolate Beam (onda)</t>
+        </is>
+      </c>
+      <c r="P67" s="7" t="inlineStr">
+        <is>
+          <t>Lightning Arrow (onda)</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="15" customHeight="1" s="8">
       <c r="A68" s="12" t="inlineStr">
@@ -3830,6 +5697,35 @@
           <t>Pan</t>
         </is>
       </c>
+      <c r="J68" t="n">
+        <v>3</v>
+      </c>
+      <c r="K68" t="n">
+        <v>2</v>
+      </c>
+      <c r="L68" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M68" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="7" t="inlineStr">
+        <is>
+          <t>Kamehameha (onda)</t>
+        </is>
+      </c>
+      <c r="O68" s="7" t="inlineStr">
+        <is>
+          <t>Gill Missile (impeto)</t>
+        </is>
+      </c>
+      <c r="P68" s="7" t="inlineStr">
+        <is>
+          <t>Maiden's Rage! (impeto)</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="8">
       <c r="A69" s="12" t="inlineStr">
@@ -3876,6 +5772,35 @@
           <t>Nail</t>
         </is>
       </c>
+      <c r="J69" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K69" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L69" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M69" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="7" t="inlineStr">
+        <is>
+          <t>Full Power Energy Wave (onda)</t>
+        </is>
+      </c>
+      <c r="O69" s="7" t="inlineStr">
+        <is>
+          <t>Super Explosive Wave (onda)</t>
+        </is>
+      </c>
+      <c r="P69" s="7" t="inlineStr">
+        <is>
+          <t>Mystic Flasher (impeto)</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="15" customHeight="1" s="8">
       <c r="A70" s="12" t="inlineStr">
@@ -3922,6 +5847,40 @@
           <t>Bardock</t>
         </is>
       </c>
+      <c r="J70" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K70" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L70" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="7" t="inlineStr">
+        <is>
+          <t>Full Power Energy Wave (onda)</t>
+        </is>
+      </c>
+      <c r="O70" s="7" t="inlineStr">
+        <is>
+          <t>Final Revenger (impeto)</t>
+        </is>
+      </c>
+      <c r="P70" s="7" t="inlineStr">
+        <is>
+          <t>Final Spirit Cannon (onda)</t>
+        </is>
+      </c>
+      <c r="Q70" s="7" t="inlineStr">
+        <is>
+          <t>Bardock Oozaru</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="15" customHeight="1" s="8">
       <c r="A71" s="12" t="inlineStr">
@@ -3968,6 +5927,35 @@
           <t>Bardock</t>
         </is>
       </c>
+      <c r="J71" t="n">
+        <v>5</v>
+      </c>
+      <c r="K71" t="n">
+        <v>5</v>
+      </c>
+      <c r="L71" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
+      <c r="N71" s="7" t="inlineStr">
+        <is>
+          <t>Chou Makouhou (onda)</t>
+        </is>
+      </c>
+      <c r="O71" s="7" t="inlineStr">
+        <is>
+          <t>Super Explosive Wave (onda)</t>
+        </is>
+      </c>
+      <c r="P71" s="7" t="inlineStr">
+        <is>
+          <t>Giga Meteor Storm (onda)</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="15" customHeight="1" s="8">
       <c r="A72" s="12" t="inlineStr">
@@ -4014,6 +6002,40 @@
           <t>Selypa</t>
         </is>
       </c>
+      <c r="J72" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K72" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L72" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M72" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="7" t="inlineStr">
+        <is>
+          <t>Full Power Energy Wave (onda)</t>
+        </is>
+      </c>
+      <c r="O72" s="7" t="inlineStr">
+        <is>
+          <t>Energy Ballet (onda)</t>
+        </is>
+      </c>
+      <c r="P72" s="7" t="inlineStr">
+        <is>
+          <t>Hysteric Saiyan Lady (impeto)</t>
+        </is>
+      </c>
+      <c r="Q72" s="7" t="inlineStr">
+        <is>
+          <t>Selypa Oozaru</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="15" customHeight="1" s="8">
       <c r="A73" s="12" t="inlineStr">
@@ -4060,6 +6082,35 @@
           <t>Selypa</t>
         </is>
       </c>
+      <c r="J73" t="n">
+        <v>5</v>
+      </c>
+      <c r="K73" t="n">
+        <v>5</v>
+      </c>
+      <c r="L73" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Chou Makouhou Barrage (impeto)</t>
+        </is>
+      </c>
+      <c r="O73" s="7" t="inlineStr">
+        <is>
+          <t>Gigant Rock Throw (onda)</t>
+        </is>
+      </c>
+      <c r="P73" s="7" t="inlineStr">
+        <is>
+          <t>Gigantic Saiyan Lady (impeto)</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="15" customHeight="1" s="8">
       <c r="A74" s="12" t="inlineStr">
@@ -4106,6 +6157,40 @@
           <t>Re Vegeta</t>
         </is>
       </c>
+      <c r="J74" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K74" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L74" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M74" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="7" t="inlineStr">
+        <is>
+          <t>Execution Beam (onda)</t>
+        </is>
+      </c>
+      <c r="O74" s="7" t="inlineStr">
+        <is>
+          <t>Super Energy Wave Volley (onda)</t>
+        </is>
+      </c>
+      <c r="P74" s="7" t="inlineStr">
+        <is>
+          <t>Orga Blaster (impeto)</t>
+        </is>
+      </c>
+      <c r="Q74" s="7" t="inlineStr">
+        <is>
+          <t>Re Vegeta Oozaru</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="15" customHeight="1" s="8">
       <c r="A75" s="12" t="inlineStr">
@@ -4152,6 +6237,35 @@
           <t>Re Vegeta</t>
         </is>
       </c>
+      <c r="J75" t="n">
+        <v>5</v>
+      </c>
+      <c r="K75" t="n">
+        <v>5</v>
+      </c>
+      <c r="L75" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
+      <c r="N75" s="7" t="inlineStr">
+        <is>
+          <t>Super Galick Gun (onda)</t>
+        </is>
+      </c>
+      <c r="O75" s="7" t="inlineStr">
+        <is>
+          <t>Super Explosive Wave (onda)</t>
+        </is>
+      </c>
+      <c r="P75" s="7" t="inlineStr">
+        <is>
+          <t>Chou Makouhou Barrage (onda)</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="15" customHeight="1" s="8">
       <c r="A76" s="12" t="inlineStr">
@@ -4198,6 +6312,40 @@
           <t>Raditz</t>
         </is>
       </c>
+      <c r="J76" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K76" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L76" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M76" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="7" t="inlineStr">
+        <is>
+          <t>Here's a present! (onda)</t>
+        </is>
+      </c>
+      <c r="O76" s="7" t="inlineStr">
+        <is>
+          <t>I'm A Top-class Warrior! (impeto)</t>
+        </is>
+      </c>
+      <c r="P76" s="7" t="inlineStr">
+        <is>
+          <t>Begone! (onda)</t>
+        </is>
+      </c>
+      <c r="Q76" s="7" t="inlineStr">
+        <is>
+          <t>Raditz Oozaru</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="15" customHeight="1" s="8">
       <c r="A77" s="12" t="inlineStr">
@@ -4244,6 +6392,35 @@
           <t>Raditz</t>
         </is>
       </c>
+      <c r="J77" t="n">
+        <v>5</v>
+      </c>
+      <c r="K77" t="n">
+        <v>5</v>
+      </c>
+      <c r="L77" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
+      <c r="N77" s="7" t="inlineStr">
+        <is>
+          <t>Chou Makouhou (onda)</t>
+        </is>
+      </c>
+      <c r="O77" s="7" t="inlineStr">
+        <is>
+          <t>Gigant Rock Throw (onda)</t>
+        </is>
+      </c>
+      <c r="P77" s="7" t="inlineStr">
+        <is>
+          <t>Chou Makousen (onda)</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="8">
       <c r="A78" s="12" t="inlineStr">
@@ -4290,6 +6467,40 @@
           <t>Nappa</t>
         </is>
       </c>
+      <c r="J78" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K78" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L78" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M78" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Volcano Explosion (onda)</t>
+        </is>
+      </c>
+      <c r="O78" s="7" t="inlineStr">
+        <is>
+          <t>Blazing Storm (impeto)</t>
+        </is>
+      </c>
+      <c r="P78" s="7" t="inlineStr">
+        <is>
+          <t>Kapa (onda)</t>
+        </is>
+      </c>
+      <c r="Q78" s="7" t="inlineStr">
+        <is>
+          <t>Nappa Oozaru</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="8">
       <c r="A79" s="12" t="inlineStr">
@@ -4336,6 +6547,35 @@
           <t>Nappa</t>
         </is>
       </c>
+      <c r="J79" t="n">
+        <v>5</v>
+      </c>
+      <c r="K79" t="n">
+        <v>5</v>
+      </c>
+      <c r="L79" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
+      <c r="N79" s="7" t="inlineStr">
+        <is>
+          <t>Gigant Rock Throw (onda)</t>
+        </is>
+      </c>
+      <c r="O79" s="7" t="inlineStr">
+        <is>
+          <t>Super Explosive Wave (onda)</t>
+        </is>
+      </c>
+      <c r="P79" s="7" t="inlineStr">
+        <is>
+          <t>Chou Makouhou (onda)</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="15" customHeight="1" s="8">
       <c r="A80" s="12" t="inlineStr">
@@ -4382,31 +6622,31 @@
           <t>Saibaiman</t>
         </is>
       </c>
-      <c r="J80" t="n">
-        <v>3</v>
-      </c>
-      <c r="K80" t="n">
-        <v>3</v>
-      </c>
-      <c r="L80" t="n">
-        <v>3</v>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr">
+      <c r="J80" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K80" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L80" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M80" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="7" t="inlineStr">
         <is>
           <t>Full Power Energy Wave (onda)</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr">
+      <c r="O80" s="7" t="inlineStr">
         <is>
           <t>High Speed Rush (impeto)</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr">
+      <c r="P80" s="7" t="inlineStr">
         <is>
           <t>Saibaman Bomb (impeto)</t>
         </is>
@@ -4457,6 +6697,40 @@
           <t>Zarbon</t>
         </is>
       </c>
+      <c r="J81" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K81" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L81" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M81" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="7" t="inlineStr">
+        <is>
+          <t>Shooting Star Arrow (onda)</t>
+        </is>
+      </c>
+      <c r="O81" s="7" t="inlineStr">
+        <is>
+          <t>Bloody Dance (impeto)</t>
+        </is>
+      </c>
+      <c r="P81" s="7" t="inlineStr">
+        <is>
+          <t>Elegant Blaster (onda)</t>
+        </is>
+      </c>
+      <c r="Q81" s="7" t="inlineStr">
+        <is>
+          <t>Zarbon (trasformato)</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="8">
       <c r="A82" s="12" t="inlineStr">
@@ -4503,6 +6777,35 @@
           <t>Zarbon</t>
         </is>
       </c>
+      <c r="J82" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K82" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L82" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M82" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="7" t="inlineStr">
+        <is>
+          <t>Elegant Blaster (onda)</t>
+        </is>
+      </c>
+      <c r="O82" s="7" t="inlineStr">
+        <is>
+          <t>Wild Pressure (impeto)</t>
+        </is>
+      </c>
+      <c r="P82" s="7" t="inlineStr">
+        <is>
+          <t>Monster Crush (impeto)</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="8">
       <c r="A83" s="12" t="inlineStr">
@@ -4549,6 +6852,35 @@
           <t>Dodoria</t>
         </is>
       </c>
+      <c r="J83" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K83" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L83" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M83" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="7" t="inlineStr">
+        <is>
+          <t>Chou Makouhou (onda)</t>
+        </is>
+      </c>
+      <c r="O83" s="7" t="inlineStr">
+        <is>
+          <t>Dodoria Head Breaker (impeto)</t>
+        </is>
+      </c>
+      <c r="P83" s="7" t="inlineStr">
+        <is>
+          <t>Maximum Buster (onda)</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="15" customHeight="1" s="8">
       <c r="A84" s="12" t="inlineStr">
@@ -4595,6 +6927,35 @@
           <t>Kyui</t>
         </is>
       </c>
+      <c r="J84" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K84" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L84" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M84" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Full Power Energy Wave (onda)</t>
+        </is>
+      </c>
+      <c r="O84" s="7" t="inlineStr">
+        <is>
+          <t>Full Power Energy Barrage Wave (impeto)</t>
+        </is>
+      </c>
+      <c r="P84" s="7" t="inlineStr">
+        <is>
+          <t>Ah! Lord Frieza! (impeto)</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="15" customHeight="1" s="8">
       <c r="A85" s="12" t="inlineStr">
@@ -4641,6 +7002,35 @@
           <t>Appule</t>
         </is>
       </c>
+      <c r="J85" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K85" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L85" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M85" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="7" t="inlineStr">
+        <is>
+          <t>Energy Wave (onda)</t>
+        </is>
+      </c>
+      <c r="O85" s="7" t="inlineStr">
+        <is>
+          <t>High Speed Rush (impeto)</t>
+        </is>
+      </c>
+      <c r="P85" s="7" t="inlineStr">
+        <is>
+          <t>Full Power Energy Ball (onda)</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="15" customHeight="1" s="8">
       <c r="A86" s="12" t="inlineStr">
@@ -4687,6 +7077,35 @@
           <t>Soldato di Freeza</t>
         </is>
       </c>
+      <c r="J86" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K86" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L86" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M86" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="7" t="inlineStr">
+        <is>
+          <t>Energy Wave (onda)</t>
+        </is>
+      </c>
+      <c r="O86" s="7" t="inlineStr">
+        <is>
+          <t>Energy Wave (onda)</t>
+        </is>
+      </c>
+      <c r="P86" s="7" t="inlineStr">
+        <is>
+          <t>Life-Risking Blow! (impeto)</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="15" customHeight="1" s="8">
       <c r="A87" s="12" t="inlineStr">
@@ -4733,6 +7152,35 @@
           <t>Ginyu</t>
         </is>
       </c>
+      <c r="J87" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K87" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L87" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M87" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="7" t="inlineStr">
+        <is>
+          <t>Full Power Energy Wave (onda)</t>
+        </is>
+      </c>
+      <c r="O87" s="7" t="inlineStr">
+        <is>
+          <t>Galaxy Dynamite (onda)</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Body Change (impeto, giganti)</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="15" customHeight="1" s="8">
       <c r="A88" s="12" t="inlineStr">
@@ -4779,31 +7227,31 @@
           <t>Recoome</t>
         </is>
       </c>
-      <c r="J88" t="n">
-        <v>4</v>
-      </c>
-      <c r="K88" t="n">
-        <v>4</v>
-      </c>
-      <c r="L88" t="n">
+      <c r="J88" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K88" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L88" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr">
+      <c r="M88" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="7" t="inlineStr">
         <is>
           <t>Recoome Eraser Gun (onda)</t>
         </is>
       </c>
-      <c r="O88" t="inlineStr">
+      <c r="O88" s="7" t="inlineStr">
         <is>
           <t>Recoome Renegade Bomber (onda)</t>
         </is>
       </c>
-      <c r="P88" t="inlineStr">
+      <c r="P88" s="7" t="inlineStr">
         <is>
           <t>Recoome Fighting Bomber (onda)</t>
         </is>
@@ -4854,31 +7302,31 @@
           <t>Butter</t>
         </is>
       </c>
-      <c r="J89" t="n">
-        <v>4</v>
-      </c>
-      <c r="K89" t="n">
+      <c r="J89" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K89" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="L89" t="n">
+      <c r="L89" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr">
+      <c r="M89" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="7" t="inlineStr">
         <is>
           <t>Space Mach Attack (impeto)</t>
         </is>
       </c>
-      <c r="O89" t="inlineStr">
+      <c r="O89" s="7" t="inlineStr">
         <is>
           <t>Full Power Energy Ball (onda)</t>
         </is>
       </c>
-      <c r="P89" t="inlineStr">
+      <c r="P89" s="7" t="inlineStr">
         <is>
           <t>Purple Comet Attack (impeto)</t>
         </is>
@@ -4929,6 +7377,35 @@
           <t>Jeeth</t>
         </is>
       </c>
+      <c r="J90" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K90" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L90" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M90" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="7" t="inlineStr">
+        <is>
+          <t>Full Power Energy Wave (onda)</t>
+        </is>
+      </c>
+      <c r="O90" s="7" t="inlineStr">
+        <is>
+          <t>Crusher Ball (onda)</t>
+        </is>
+      </c>
+      <c r="P90" s="7" t="inlineStr">
+        <is>
+          <t>Purple Comet Attack (impeto)</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="15" customHeight="1" s="8">
       <c r="A91" s="12" t="inlineStr">
@@ -4975,6 +7452,35 @@
           <t>Guldo</t>
         </is>
       </c>
+      <c r="J91" t="n">
+        <v>3</v>
+      </c>
+      <c r="K91" t="n">
+        <v>2</v>
+      </c>
+      <c r="L91" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M91" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="7" t="inlineStr">
+        <is>
+          <t>Psychic Rock Throw (impeto)</t>
+        </is>
+      </c>
+      <c r="O91" s="7" t="inlineStr">
+        <is>
+          <t>Full Power Energy Blast Volley (onda)</t>
+        </is>
+      </c>
+      <c r="P91" s="7" t="inlineStr">
+        <is>
+          <t>Guldo Special (impeto)</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="15" customHeight="1" s="8">
       <c r="A92" s="12" t="inlineStr">
@@ -5018,7 +7524,41 @@
       </c>
       <c r="I92" s="12" t="inlineStr">
         <is>
-          <t>Freeza</t>
+          <t>Freeza (prima forma)</t>
+        </is>
+      </c>
+      <c r="J92" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K92" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L92" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M92" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="7" t="inlineStr">
+        <is>
+          <t>Death Beam (onda)</t>
+        </is>
+      </c>
+      <c r="O92" s="7" t="inlineStr">
+        <is>
+          <t>Punishing Rush (impeto)</t>
+        </is>
+      </c>
+      <c r="P92" s="7" t="inlineStr">
+        <is>
+          <t>Death Ball (onda)</t>
+        </is>
+      </c>
+      <c r="Q92" s="7" t="inlineStr">
+        <is>
+          <t>Freeza (seconda forma)</t>
         </is>
       </c>
     </row>
@@ -5064,7 +7604,41 @@
       </c>
       <c r="I93" s="12" t="inlineStr">
         <is>
-          <t>Freeza</t>
+          <t>Freeza (prima forma)</t>
+        </is>
+      </c>
+      <c r="J93" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K93" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L93" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M93" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="7" t="inlineStr">
+        <is>
+          <t>Punishing Blaster (onda)</t>
+        </is>
+      </c>
+      <c r="O93" s="7" t="inlineStr">
+        <is>
+          <t>Death Storm (onda)</t>
+        </is>
+      </c>
+      <c r="P93" s="7" t="inlineStr">
+        <is>
+          <t>HAIL Frieza (impeto)</t>
+        </is>
+      </c>
+      <c r="Q93" s="7" t="inlineStr">
+        <is>
+          <t>Freeza (terza forma)</t>
         </is>
       </c>
     </row>
@@ -5110,7 +7684,41 @@
       </c>
       <c r="I94" s="12" t="inlineStr">
         <is>
-          <t>Freeza</t>
+          <t>Freeza (prima forma)</t>
+        </is>
+      </c>
+      <c r="J94" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K94" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L94" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M94" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="7" t="inlineStr">
+        <is>
+          <t>Death Beam (onda)</t>
+        </is>
+      </c>
+      <c r="O94" s="7" t="inlineStr">
+        <is>
+          <t>High Speed Rush (impeto)</t>
+        </is>
+      </c>
+      <c r="P94" s="7" t="inlineStr">
+        <is>
+          <t>Crazy Finger Beam (onda)</t>
+        </is>
+      </c>
+      <c r="Q94" s="7" t="inlineStr">
+        <is>
+          <t>Freeza (forma finale)</t>
         </is>
       </c>
     </row>
@@ -5156,7 +7764,41 @@
       </c>
       <c r="I95" s="12" t="inlineStr">
         <is>
-          <t>Freeza</t>
+          <t>Freeza (prima forma)</t>
+        </is>
+      </c>
+      <c r="J95" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K95" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L95" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M95" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="7" t="inlineStr">
+        <is>
+          <t>Barrage Death Beam (onda)</t>
+        </is>
+      </c>
+      <c r="O95" s="7" t="inlineStr">
+        <is>
+          <t>I Might Die This Time. (onda)</t>
+        </is>
+      </c>
+      <c r="P95" s="7" t="inlineStr">
+        <is>
+          <t>Destroy The Planet! (onda)</t>
+        </is>
+      </c>
+      <c r="Q95" s="7" t="inlineStr">
+        <is>
+          <t>Freeza (massima potenza)</t>
         </is>
       </c>
     </row>
@@ -5202,7 +7844,36 @@
       </c>
       <c r="I96" s="12" t="inlineStr">
         <is>
-          <t>Freeza</t>
+          <t>Freeza (prima forma)</t>
+        </is>
+      </c>
+      <c r="J96" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K96" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L96" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M96" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="7" t="inlineStr">
+        <is>
+          <t>Death Saucer (onda)</t>
+        </is>
+      </c>
+      <c r="O96" s="7" t="inlineStr">
+        <is>
+          <t>Nova Strike (impeto)</t>
+        </is>
+      </c>
+      <c r="P96" s="7" t="inlineStr">
+        <is>
+          <t>You Will Die By My Hand! (onda)</t>
         </is>
       </c>
     </row>
@@ -5248,7 +7919,36 @@
       </c>
       <c r="I97" s="12" t="inlineStr">
         <is>
-          <t>Freeza</t>
+          <t>Mecha Freeza</t>
+        </is>
+      </c>
+      <c r="J97" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K97" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L97" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M97" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="7" t="inlineStr">
+        <is>
+          <t>Death Beam (onda)</t>
+        </is>
+      </c>
+      <c r="O97" s="7" t="inlineStr">
+        <is>
+          <t>Fissure Slash (onda)</t>
+        </is>
+      </c>
+      <c r="P97" s="7" t="inlineStr">
+        <is>
+          <t>Supernova (onda)</t>
         </is>
       </c>
     </row>
@@ -5297,6 +7997,35 @@
           <t>Re Cold</t>
         </is>
       </c>
+      <c r="J98" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K98" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L98" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M98" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="7" t="inlineStr">
+        <is>
+          <t>Full Power Death Beam (onda)</t>
+        </is>
+      </c>
+      <c r="O98" s="7" t="inlineStr">
+        <is>
+          <t>Super Explosive Wave (onda)</t>
+        </is>
+      </c>
+      <c r="P98" s="7" t="inlineStr">
+        <is>
+          <t>Cold Family Power (impeto)</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="15" customHeight="1" s="8">
       <c r="A99" s="12" t="inlineStr">
@@ -5343,6 +8072,35 @@
           <t>C-16</t>
         </is>
       </c>
+      <c r="J99" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K99" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L99" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M99" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="7" t="inlineStr">
+        <is>
+          <t>Hell's Impact (impeto)</t>
+        </is>
+      </c>
+      <c r="O99" s="7" t="inlineStr">
+        <is>
+          <t>Hell's Flash (impeto)</t>
+        </is>
+      </c>
+      <c r="P99" s="7" t="inlineStr">
+        <is>
+          <t>Self Destruct Device (impeto)</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="15" customHeight="1" s="8">
       <c r="A100" s="12" t="inlineStr">
@@ -5389,6 +8147,35 @@
           <t>C-17</t>
         </is>
       </c>
+      <c r="J100" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K100" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L100" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M100" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="7" t="inlineStr">
+        <is>
+          <t>Full Power Energy Ball (onda)</t>
+        </is>
+      </c>
+      <c r="O100" s="7" t="inlineStr">
+        <is>
+          <t>Photon Flash (onda)</t>
+        </is>
+      </c>
+      <c r="P100" s="7" t="inlineStr">
+        <is>
+          <t>Sadistic Dance (impeto)</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="15" customHeight="1" s="8">
       <c r="A101" s="12" t="inlineStr">
@@ -5435,6 +8222,35 @@
           <t>C-18</t>
         </is>
       </c>
+      <c r="J101" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K101" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L101" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M101" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="7" t="inlineStr">
+        <is>
+          <t>Infinity Bullet (onda)</t>
+        </is>
+      </c>
+      <c r="O101" s="7" t="inlineStr">
+        <is>
+          <t>Destructo Disc (onda)</t>
+        </is>
+      </c>
+      <c r="P101" s="7" t="inlineStr">
+        <is>
+          <t>Sadistic 18 (impeto)</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="15" customHeight="1" s="8">
       <c r="A102" s="12" t="inlineStr">
@@ -5481,6 +8297,35 @@
           <t>C-19</t>
         </is>
       </c>
+      <c r="J102" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K102" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L102" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M102" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N102" s="7" t="inlineStr">
+        <is>
+          <t>Full Power Energy Wave (onda)</t>
+        </is>
+      </c>
+      <c r="O102" s="7" t="inlineStr">
+        <is>
+          <t>High Power Rush (impeto)</t>
+        </is>
+      </c>
+      <c r="P102" s="7" t="inlineStr">
+        <is>
+          <t>Drain Life 19 (impeto)</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="15" customHeight="1" s="8">
       <c r="A103" s="12" t="inlineStr">
@@ -5524,7 +8369,36 @@
       </c>
       <c r="I103" s="12" t="inlineStr">
         <is>
-          <t>Dr. Gero</t>
+          <t>Dr. Gero (C-20)</t>
+        </is>
+      </c>
+      <c r="J103" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K103" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L103" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M103" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="7" t="inlineStr">
+        <is>
+          <t>Full Power Energy Wave (onda)</t>
+        </is>
+      </c>
+      <c r="O103" s="7" t="inlineStr">
+        <is>
+          <t>Bionic Punisher (onda)</t>
+        </is>
+      </c>
+      <c r="P103" s="7" t="inlineStr">
+        <is>
+          <t>Drain Life 20 (impeto)</t>
         </is>
       </c>
     </row>
@@ -5570,7 +8444,41 @@
       </c>
       <c r="I104" s="12" t="inlineStr">
         <is>
-          <t>Cell</t>
+          <t>Cell (prima forma)</t>
+        </is>
+      </c>
+      <c r="J104" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K104" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L104" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M104" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="7" t="inlineStr">
+        <is>
+          <t>Kamehameha (onda)</t>
+        </is>
+      </c>
+      <c r="O104" s="7" t="inlineStr">
+        <is>
+          <t>Special Beam Cannon (onda)</t>
+        </is>
+      </c>
+      <c r="P104" s="7" t="inlineStr">
+        <is>
+          <t>Drain Life Cell (impeto)</t>
+        </is>
+      </c>
+      <c r="Q104" s="7" t="inlineStr">
+        <is>
+          <t>Cell (seconda forma)</t>
         </is>
       </c>
     </row>
@@ -5616,7 +8524,41 @@
       </c>
       <c r="I105" s="12" t="inlineStr">
         <is>
-          <t>Cell</t>
+          <t>Cell (prima forma)</t>
+        </is>
+      </c>
+      <c r="J105" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K105" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L105" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M105" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="7" t="inlineStr">
+        <is>
+          <t>Big Bang Crash (onda)</t>
+        </is>
+      </c>
+      <c r="O105" s="7" t="inlineStr">
+        <is>
+          <t>Drain Life Cell (impeto)</t>
+        </is>
+      </c>
+      <c r="P105" s="7" t="inlineStr">
+        <is>
+          <t>Unforgivable! (impeto)</t>
+        </is>
+      </c>
+      <c r="Q105" s="7" t="inlineStr">
+        <is>
+          <t>Cell (forma perfetta)</t>
         </is>
       </c>
     </row>
@@ -5662,7 +8604,41 @@
       </c>
       <c r="I106" s="12" t="inlineStr">
         <is>
-          <t>Cell</t>
+          <t>Cell (prima forma)</t>
+        </is>
+      </c>
+      <c r="J106" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K106" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L106" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M106" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N106" s="7" t="inlineStr">
+        <is>
+          <t>Super Kamehameha (onda)</t>
+        </is>
+      </c>
+      <c r="O106" s="7" t="inlineStr">
+        <is>
+          <t>Barrage Death Beam (onda)</t>
+        </is>
+      </c>
+      <c r="P106" s="7" t="inlineStr">
+        <is>
+          <t>Perfect Barrier (onda)</t>
+        </is>
+      </c>
+      <c r="Q106" s="7" t="inlineStr">
+        <is>
+          <t>Cell (perfetto, massima potenza)</t>
         </is>
       </c>
     </row>
@@ -5708,7 +8684,36 @@
       </c>
       <c r="I107" s="12" t="inlineStr">
         <is>
-          <t>Cell</t>
+          <t>Cell (prima forma)</t>
+        </is>
+      </c>
+      <c r="J107" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K107" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L107" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M107" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="7" t="inlineStr">
+        <is>
+          <t>Full Power Death Beam (onda)</t>
+        </is>
+      </c>
+      <c r="O107" s="7" t="inlineStr">
+        <is>
+          <t>Perfect Combination (impeto)</t>
+        </is>
+      </c>
+      <c r="P107" s="7" t="inlineStr">
+        <is>
+          <t>Solar Kamehameha (onda)</t>
         </is>
       </c>
     </row>
@@ -5757,31 +8762,31 @@
           <t>Cell Jr.</t>
         </is>
       </c>
-      <c r="J108" t="n">
-        <v>3</v>
-      </c>
-      <c r="K108" t="n">
+      <c r="J108" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K108" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="L108" t="n">
-        <v>4</v>
-      </c>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr">
+      <c r="L108" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M108" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" s="7" t="inlineStr">
         <is>
           <t>Special Beam Cannon (onda)</t>
         </is>
       </c>
-      <c r="O108" t="inlineStr">
+      <c r="O108" s="7" t="inlineStr">
         <is>
           <t>Innocence Rush (impeto)</t>
         </is>
       </c>
-      <c r="P108" t="inlineStr">
+      <c r="P108" s="7" t="inlineStr">
         <is>
           <t>Super Kamehameha (onda)</t>
         </is>
@@ -5829,7 +8834,36 @@
       </c>
       <c r="I109" s="12" t="inlineStr">
         <is>
-          <t>Majin Buu</t>
+          <t>Majin Buu (buono)</t>
+        </is>
+      </c>
+      <c r="J109" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K109" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L109" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M109" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N109" s="7" t="inlineStr">
+        <is>
+          <t>Flame Shower Breath (onda)</t>
+        </is>
+      </c>
+      <c r="O109" s="7" t="inlineStr">
+        <is>
+          <t>Super Kamehameha (onda)</t>
+        </is>
+      </c>
+      <c r="P109" s="7" t="inlineStr">
+        <is>
+          <t>Angry Explosion (onda)</t>
         </is>
       </c>
     </row>
@@ -5875,7 +8909,36 @@
       </c>
       <c r="I110" s="12" t="inlineStr">
         <is>
-          <t>Majin Buu</t>
+          <t>Majin Buu (puro male)</t>
+        </is>
+      </c>
+      <c r="J110" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K110" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L110" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M110" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="7" t="inlineStr">
+        <is>
+          <t>Super Kamehameha (onda)</t>
+        </is>
+      </c>
+      <c r="O110" s="7" t="inlineStr">
+        <is>
+          <t>Flame Shower Breath (onda)</t>
+        </is>
+      </c>
+      <c r="P110" s="7" t="inlineStr">
+        <is>
+          <t>Super Explosive Wave (onda)</t>
         </is>
       </c>
     </row>
@@ -5921,7 +8984,41 @@
       </c>
       <c r="I111" s="12" t="inlineStr">
         <is>
-          <t>Majin Buu</t>
+          <t>Super Buu</t>
+        </is>
+      </c>
+      <c r="J111" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K111" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L111" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M111" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" s="7" t="inlineStr">
+        <is>
+          <t>Genocide Blast (onda)</t>
+        </is>
+      </c>
+      <c r="O111" s="7" t="inlineStr">
+        <is>
+          <t>Chocolate Beam (onda)</t>
+        </is>
+      </c>
+      <c r="P111" s="7" t="inlineStr">
+        <is>
+          <t>Revenge Death Bomber (onda)</t>
+        </is>
+      </c>
+      <c r="Q111" s="7" t="inlineStr">
+        <is>
+          <t>Super Buu (Gotenks assorbito)</t>
         </is>
       </c>
     </row>
@@ -5967,7 +9064,41 @@
       </c>
       <c r="I112" s="12" t="inlineStr">
         <is>
-          <t>Majin Buu</t>
+          <t>Super Buu</t>
+        </is>
+      </c>
+      <c r="J112" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K112" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L112" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M112" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N112" s="7" t="inlineStr">
+        <is>
+          <t>Galactic Donut Volley (onda)</t>
+        </is>
+      </c>
+      <c r="O112" s="7" t="inlineStr">
+        <is>
+          <t>Special Beam Cannon (onda)</t>
+        </is>
+      </c>
+      <c r="P112" s="7" t="inlineStr">
+        <is>
+          <t>Super Kamehameha (onda)</t>
+        </is>
+      </c>
+      <c r="Q112" s="7" t="inlineStr">
+        <is>
+          <t>Super Buu (Son Gohan assorbito)</t>
         </is>
       </c>
     </row>
@@ -6013,7 +9144,36 @@
       </c>
       <c r="I113" s="12" t="inlineStr">
         <is>
-          <t>Majin Buu</t>
+          <t>Super Buu</t>
+        </is>
+      </c>
+      <c r="J113" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K113" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L113" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M113" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="7" t="inlineStr">
+        <is>
+          <t>Super Kamehameha (onda)</t>
+        </is>
+      </c>
+      <c r="O113" s="7" t="inlineStr">
+        <is>
+          <t>Chocolate Beam (onda)</t>
+        </is>
+      </c>
+      <c r="P113" s="7" t="inlineStr">
+        <is>
+          <t>Super Ghost Buu Attack (onda)</t>
         </is>
       </c>
     </row>
@@ -6059,7 +9219,36 @@
       </c>
       <c r="I114" s="12" t="inlineStr">
         <is>
-          <t>Majin Buu</t>
+          <t>Majin Buu (puro)</t>
+        </is>
+      </c>
+      <c r="J114" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K114" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L114" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M114" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N114" s="7" t="inlineStr">
+        <is>
+          <t>Super Kamehameha (onda)</t>
+        </is>
+      </c>
+      <c r="O114" s="7" t="inlineStr">
+        <is>
+          <t>Mystic Combination (impeto)</t>
+        </is>
+      </c>
+      <c r="P114" s="7" t="inlineStr">
+        <is>
+          <t>Planet Burst (onda)</t>
         </is>
       </c>
     </row>
@@ -6108,6 +9297,35 @@
           <t>Dabura</t>
         </is>
       </c>
+      <c r="J115" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K115" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L115" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M115" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" s="7" t="inlineStr">
+        <is>
+          <t>Evil Impulse (onda)</t>
+        </is>
+      </c>
+      <c r="O115" s="7" t="inlineStr">
+        <is>
+          <t>Evil Flame (onda)</t>
+        </is>
+      </c>
+      <c r="P115" s="7" t="inlineStr">
+        <is>
+          <t>Darkness Sword Attack (impeto)</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="15" customHeight="1" s="8">
       <c r="A116" s="12" t="inlineStr">
@@ -6154,6 +9372,35 @@
           <t>Bobbidi</t>
         </is>
       </c>
+      <c r="J116" t="n">
+        <v>3</v>
+      </c>
+      <c r="K116" t="n">
+        <v>2</v>
+      </c>
+      <c r="L116" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M116" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N116" s="7" t="inlineStr">
+        <is>
+          <t>Pui Pui Nice Shot (impeto)</t>
+        </is>
+      </c>
+      <c r="O116" s="7" t="inlineStr">
+        <is>
+          <t>Yakon Is Next! (impeto)</t>
+        </is>
+      </c>
+      <c r="P116" s="7" t="inlineStr">
+        <is>
+          <t>Babidi's Ultimate Power (onda)</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="15" customHeight="1" s="8">
       <c r="A117" s="12" t="inlineStr">
@@ -6200,6 +9447,35 @@
           <t>Spopovitch</t>
         </is>
       </c>
+      <c r="J117" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K117" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L117" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M117" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" s="7" t="inlineStr">
+        <is>
+          <t>Berserker Crash (impeto)</t>
+        </is>
+      </c>
+      <c r="O117" s="7" t="inlineStr">
+        <is>
+          <t>Mad Banquet (impeto)</t>
+        </is>
+      </c>
+      <c r="P117" s="7" t="inlineStr">
+        <is>
+          <t>Majin Buu Resurrection (impeto)</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="15" customHeight="1" s="8">
       <c r="A118" s="12" t="inlineStr">
@@ -6246,6 +9522,35 @@
           <t>Paikuhan</t>
         </is>
       </c>
+      <c r="J118" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K118" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L118" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M118" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N118" s="7" t="inlineStr">
+        <is>
+          <t>Hyper Tornado (impeto)</t>
+        </is>
+      </c>
+      <c r="O118" s="7" t="inlineStr">
+        <is>
+          <t>Burning Shoot (impeto)</t>
+        </is>
+      </c>
+      <c r="P118" s="7" t="inlineStr">
+        <is>
+          <t>Thunder Flash (onda)</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="15" customHeight="1" s="8">
       <c r="A119" s="12" t="inlineStr">
@@ -6292,6 +9597,40 @@
           <t>Garlic Jr.</t>
         </is>
       </c>
+      <c r="J119" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K119" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L119" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M119" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="7" t="inlineStr">
+        <is>
+          <t>Darkness Eye Beam (onda)</t>
+        </is>
+      </c>
+      <c r="O119" s="7" t="inlineStr">
+        <is>
+          <t>High Speed Rush (impeto)</t>
+        </is>
+      </c>
+      <c r="P119" s="7" t="inlineStr">
+        <is>
+          <t>Full Power Energy Ball (onda)</t>
+        </is>
+      </c>
+      <c r="Q119" s="7" t="inlineStr">
+        <is>
+          <t>Super Garlic Jr.</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="15" customHeight="1" s="8">
       <c r="A120" s="12" t="inlineStr">
@@ -6338,6 +9677,35 @@
           <t>Garlic Jr.</t>
         </is>
       </c>
+      <c r="J120" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K120" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L120" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N120" s="7" t="inlineStr">
+        <is>
+          <t>Death Impact (onda)</t>
+        </is>
+      </c>
+      <c r="O120" s="7" t="inlineStr">
+        <is>
+          <t>Darkness Illusion (impeto)</t>
+        </is>
+      </c>
+      <c r="P120" s="7" t="inlineStr">
+        <is>
+          <t>Dead Zone (onda)</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="15" customHeight="1" s="8">
       <c r="A121" s="12" t="inlineStr">
@@ -6384,6 +9752,35 @@
           <t>Dr. Uiro</t>
         </is>
       </c>
+      <c r="J121" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K121" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L121" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M121" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="7" t="inlineStr">
+        <is>
+          <t>Photon Strike (onda)</t>
+        </is>
+      </c>
+      <c r="O121" s="7" t="inlineStr">
+        <is>
+          <t>Gigantic Bomber (impeto)</t>
+        </is>
+      </c>
+      <c r="P121" s="7" t="inlineStr">
+        <is>
+          <t>Planet Geyser (onda)</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="15" customHeight="1" s="8">
       <c r="A122" s="12" t="inlineStr">
@@ -6430,6 +9827,40 @@
           <t>Turles</t>
         </is>
       </c>
+      <c r="J122" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K122" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L122" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M122" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N122" s="7" t="inlineStr">
+        <is>
+          <t>Kill Driver (onda)</t>
+        </is>
+      </c>
+      <c r="O122" s="7" t="inlineStr">
+        <is>
+          <t>Full Power Energy Barrage Wave (onda)</t>
+        </is>
+      </c>
+      <c r="P122" s="7" t="inlineStr">
+        <is>
+          <t>Meteor Burst (impeto)</t>
+        </is>
+      </c>
+      <c r="Q122" s="7" t="inlineStr">
+        <is>
+          <t>Turles Oozaru</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="15" customHeight="1" s="8">
       <c r="A123" s="12" t="inlineStr">
@@ -6476,6 +9907,35 @@
           <t>Turles</t>
         </is>
       </c>
+      <c r="J123" t="n">
+        <v>5</v>
+      </c>
+      <c r="K123" t="n">
+        <v>5</v>
+      </c>
+      <c r="L123" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
+      <c r="N123" s="7" t="inlineStr">
+        <is>
+          <t>Chou Makouhou (onda)</t>
+        </is>
+      </c>
+      <c r="O123" s="7" t="inlineStr">
+        <is>
+          <t>Chou Makouhou Barrage (onda)</t>
+        </is>
+      </c>
+      <c r="P123" s="7" t="inlineStr">
+        <is>
+          <t>Chou Makousen (onda)</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="15" customHeight="1" s="8">
       <c r="A124" s="12" t="inlineStr">
@@ -6522,6 +9982,40 @@
           <t>Slug</t>
         </is>
       </c>
+      <c r="J124" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K124" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L124" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M124" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N124" s="7" t="inlineStr">
+        <is>
+          <t>Finger Beam (onda)</t>
+        </is>
+      </c>
+      <c r="O124" s="7" t="inlineStr">
+        <is>
+          <t>Darkness Eye Beam (onda)</t>
+        </is>
+      </c>
+      <c r="P124" s="7" t="inlineStr">
+        <is>
+          <t>Power of Darkness (impeto)</t>
+        </is>
+      </c>
+      <c r="Q124" s="7" t="inlineStr">
+        <is>
+          <t>Slug (gigante)</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="15" customHeight="1" s="8">
       <c r="A125" s="12" t="inlineStr">
@@ -6568,6 +10062,35 @@
           <t>Slug</t>
         </is>
       </c>
+      <c r="J125" t="n">
+        <v>5</v>
+      </c>
+      <c r="K125" t="n">
+        <v>5</v>
+      </c>
+      <c r="L125" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
+      <c r="N125" s="7" t="inlineStr">
+        <is>
+          <t>Darkness Eye Beam (onda)</t>
+        </is>
+      </c>
+      <c r="O125" s="7" t="inlineStr">
+        <is>
+          <t>Super Explosive Wave (onda)</t>
+        </is>
+      </c>
+      <c r="P125" s="7" t="inlineStr">
+        <is>
+          <t>Darkness Blaster (onda)</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="15" customHeight="1" s="8">
       <c r="A126" s="12" t="inlineStr">
@@ -6614,6 +10137,35 @@
           <t>Sauzer</t>
         </is>
       </c>
+      <c r="J126" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K126" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L126" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M126" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N126" s="7" t="inlineStr">
+        <is>
+          <t>Full Power Energy Wave (onda)</t>
+        </is>
+      </c>
+      <c r="O126" s="7" t="inlineStr">
+        <is>
+          <t>Scatter Finger Beam (onda)</t>
+        </is>
+      </c>
+      <c r="P126" s="7" t="inlineStr">
+        <is>
+          <t>Salza Blade Rush (impeto)</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="15" customHeight="1" s="8">
       <c r="A127" s="12" t="inlineStr">
@@ -6660,6 +10212,40 @@
           <t>Cooler</t>
         </is>
       </c>
+      <c r="J127" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K127" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L127" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M127" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="7" t="inlineStr">
+        <is>
+          <t>Full Power Energy Wave (onda)</t>
+        </is>
+      </c>
+      <c r="O127" s="7" t="inlineStr">
+        <is>
+          <t>Darkness Eye Beam (onda)</t>
+        </is>
+      </c>
+      <c r="P127" s="7" t="inlineStr">
+        <is>
+          <t>Death Ball (onda)</t>
+        </is>
+      </c>
+      <c r="Q127" s="7" t="inlineStr">
+        <is>
+          <t>Cooler (forma finale)</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="15" customHeight="1" s="8">
       <c r="A128" s="12" t="inlineStr">
@@ -6706,6 +10292,35 @@
           <t>Cooler</t>
         </is>
       </c>
+      <c r="J128" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K128" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L128" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M128" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N128" s="7" t="inlineStr">
+        <is>
+          <t>Death Beam (onda)</t>
+        </is>
+      </c>
+      <c r="O128" s="7" t="inlineStr">
+        <is>
+          <t>Death Chaser (impeto)</t>
+        </is>
+      </c>
+      <c r="P128" s="7" t="inlineStr">
+        <is>
+          <t>Supernova (onda)</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="15" customHeight="1" s="8">
       <c r="A129" s="12" t="inlineStr">
@@ -6749,7 +10364,36 @@
       </c>
       <c r="I129" s="12" t="inlineStr">
         <is>
-          <t>Cooler</t>
+          <t>Metal Cooler</t>
+        </is>
+      </c>
+      <c r="J129" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K129" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L129" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M129" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N129" s="7" t="inlineStr">
+        <is>
+          <t>Lock-On Buster (onda)</t>
+        </is>
+      </c>
+      <c r="O129" s="7" t="inlineStr">
+        <is>
+          <t>Finger Blitz Barrage (onda)</t>
+        </is>
+      </c>
+      <c r="P129" s="7" t="inlineStr">
+        <is>
+          <t>Supernova (onda)</t>
         </is>
       </c>
     </row>
@@ -6798,6 +10442,40 @@
           <t>C-13</t>
         </is>
       </c>
+      <c r="J130" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K130" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L130" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M130" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N130" s="7" t="inlineStr">
+        <is>
+          <t>Full Power Energy Wave (onda)</t>
+        </is>
+      </c>
+      <c r="O130" s="7" t="inlineStr">
+        <is>
+          <t>Silent Assassin 13 (impeto)</t>
+        </is>
+      </c>
+      <c r="P130" s="7" t="inlineStr">
+        <is>
+          <t>S.S. Deadly Bomber (onda)</t>
+        </is>
+      </c>
+      <c r="Q130" s="7" t="inlineStr">
+        <is>
+          <t>Super C-13</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="15" customHeight="1" s="8">
       <c r="A131" s="12" t="inlineStr">
@@ -6844,6 +10522,35 @@
           <t>C-13</t>
         </is>
       </c>
+      <c r="J131" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K131" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L131" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M131" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N131" s="7" t="inlineStr">
+        <is>
+          <t>S.S. Deadly Bomber (onda)</t>
+        </is>
+      </c>
+      <c r="O131" s="7" t="inlineStr">
+        <is>
+          <t>Super Explosive Wave (onda)</t>
+        </is>
+      </c>
+      <c r="P131" s="7" t="inlineStr">
+        <is>
+          <t>S.S. Deadly Hammer (impeto)</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="15" customHeight="1" s="8">
       <c r="A132" s="12" t="inlineStr">
@@ -6890,6 +10597,40 @@
           <t>Broli</t>
         </is>
       </c>
+      <c r="J132" t="n">
+        <v>5</v>
+      </c>
+      <c r="K132" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L132" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M132" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N132" s="7" t="inlineStr">
+        <is>
+          <t>Full Power Energy Wave (onda)</t>
+        </is>
+      </c>
+      <c r="O132" s="7" t="inlineStr">
+        <is>
+          <t>Bloody Smash (impeto)</t>
+        </is>
+      </c>
+      <c r="P132" s="7" t="inlineStr">
+        <is>
+          <t>Eraser Cannon (onda)</t>
+        </is>
+      </c>
+      <c r="Q132" s="7" t="inlineStr">
+        <is>
+          <t>Broli SSJ</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="15" customHeight="1" s="8">
       <c r="A133" s="12" t="inlineStr">
@@ -6936,6 +10677,40 @@
           <t>Broli</t>
         </is>
       </c>
+      <c r="J133" t="n">
+        <v>5</v>
+      </c>
+      <c r="K133" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L133" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M133" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N133" s="7" t="inlineStr">
+        <is>
+          <t>Eraser Cannon (onda)</t>
+        </is>
+      </c>
+      <c r="O133" s="7" t="inlineStr">
+        <is>
+          <t>Trap Shooter (onda)</t>
+        </is>
+      </c>
+      <c r="P133" s="7" t="inlineStr">
+        <is>
+          <t>Super Explosive Wave (onda)</t>
+        </is>
+      </c>
+      <c r="Q133" s="7" t="inlineStr">
+        <is>
+          <t>Broli Super Saiyan Leggendario</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="15" customHeight="1" s="8">
       <c r="A134" s="12" t="inlineStr">
@@ -6954,7 +10729,7 @@
       </c>
       <c r="D134" s="12" t="inlineStr">
         <is>
-          <t>SS-</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="E134" s="12" t="inlineStr">
@@ -6982,31 +10757,31 @@
           <t>Broli</t>
         </is>
       </c>
-      <c r="J134" t="n">
+      <c r="J134" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="K134" t="n">
-        <v>4</v>
-      </c>
-      <c r="L134" t="n">
+      <c r="K134" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L134" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N134" t="inlineStr">
+      <c r="M134" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N134" s="7" t="inlineStr">
         <is>
           <t>Eraser Cannon (onda)</t>
         </is>
       </c>
-      <c r="O134" t="inlineStr">
+      <c r="O134" s="7" t="inlineStr">
         <is>
           <t>Gigantic Hammer (impeto)</t>
         </is>
       </c>
-      <c r="P134" t="inlineStr">
+      <c r="P134" s="7" t="inlineStr">
         <is>
           <t>Omega Blaster (onda)</t>
         </is>
@@ -7057,6 +10832,35 @@
           <t>Zangya</t>
         </is>
       </c>
+      <c r="J135" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K135" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L135" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M135" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>Shoot Blaster (onda)</t>
+        </is>
+      </c>
+      <c r="O135" s="7" t="inlineStr">
+        <is>
+          <t>Trap Shooter (impeto)</t>
+        </is>
+      </c>
+      <c r="P135" s="7" t="inlineStr">
+        <is>
+          <t>Sky Zapper (impeto)</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="15" customHeight="1" s="8">
       <c r="A136" s="12" t="inlineStr">
@@ -7103,6 +10907,40 @@
           <t>Bojack</t>
         </is>
       </c>
+      <c r="J136" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K136" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L136" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M136" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N136" s="7" t="inlineStr">
+        <is>
+          <t>Full Power Energy Ball (onda)</t>
+        </is>
+      </c>
+      <c r="O136" s="7" t="inlineStr">
+        <is>
+          <t>Trap Shooter (onda)</t>
+        </is>
+      </c>
+      <c r="P136" s="7" t="inlineStr">
+        <is>
+          <t>Grand Smasher (onda)</t>
+        </is>
+      </c>
+      <c r="Q136" s="7" t="inlineStr">
+        <is>
+          <t>Bojack (massima potenza)</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="15" customHeight="1" s="8">
       <c r="A137" s="12" t="inlineStr">
@@ -7149,6 +10987,35 @@
           <t>Bojack</t>
         </is>
       </c>
+      <c r="J137" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K137" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L137" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M137" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N137" s="7" t="inlineStr">
+        <is>
+          <t>Grand Smasher (onda)</t>
+        </is>
+      </c>
+      <c r="O137" s="7" t="inlineStr">
+        <is>
+          <t>Galactic Tyrant (impeto)</t>
+        </is>
+      </c>
+      <c r="P137" s="7" t="inlineStr">
+        <is>
+          <t>Galactic Buster (onda)</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="15" customHeight="1" s="8">
       <c r="A138" s="12" t="inlineStr">
@@ -7195,6 +11062,40 @@
           <t>Janemba</t>
         </is>
       </c>
+      <c r="J138" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K138" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L138" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M138" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N138" s="7" t="inlineStr">
+        <is>
+          <t>Chou Makouhou (onda)</t>
+        </is>
+      </c>
+      <c r="O138" s="7" t="inlineStr">
+        <is>
+          <t>Rapid Cannon (onda)</t>
+        </is>
+      </c>
+      <c r="P138" s="7" t="inlineStr">
+        <is>
+          <t>Illusion Smash (impeto)</t>
+        </is>
+      </c>
+      <c r="Q138" s="7" t="inlineStr">
+        <is>
+          <t>Super Janemba</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="15" customHeight="1" s="8">
       <c r="A139" s="12" t="inlineStr">
@@ -7241,6 +11142,35 @@
           <t>Janemba</t>
         </is>
       </c>
+      <c r="J139" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K139" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L139" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M139" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>Chou Makouhou (onda)</t>
+        </is>
+      </c>
+      <c r="O139" s="7" t="inlineStr">
+        <is>
+          <t>Lightning Shower Rain (impeto)</t>
+        </is>
+      </c>
+      <c r="P139" s="7" t="inlineStr">
+        <is>
+          <t>Dimension Sword Attack (impeto)</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="15" customHeight="1" s="8">
       <c r="A140" s="12" t="inlineStr">
@@ -7287,31 +11217,31 @@
           <t>Hildegarn</t>
         </is>
       </c>
-      <c r="J140" t="n">
+      <c r="J140" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="K140" t="n">
+      <c r="K140" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="L140" t="n">
+      <c r="L140" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="M140" t="inlineStr">
+      <c r="M140" s="7" t="inlineStr">
         <is>
           <t>sì</t>
         </is>
       </c>
-      <c r="N140" t="inlineStr">
+      <c r="N140" s="7" t="inlineStr">
         <is>
           <t>Chou Makousen (onda)</t>
         </is>
       </c>
-      <c r="O140" t="inlineStr">
+      <c r="O140" s="7" t="inlineStr">
         <is>
           <t>Super Explosive Wave (onda)</t>
         </is>
       </c>
-      <c r="P140" t="inlineStr">
+      <c r="P140" s="7" t="inlineStr">
         <is>
           <t>Gigantic Flame (onda)</t>
         </is>
@@ -7362,6 +11292,35 @@
           <t>Tapion</t>
         </is>
       </c>
+      <c r="J141" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K141" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L141" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M141" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N141" s="7" t="inlineStr">
+        <is>
+          <t>Brave Cannon (onda)</t>
+        </is>
+      </c>
+      <c r="O141" s="7" t="inlineStr">
+        <is>
+          <t>Brave Slash (onda)</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Brave Sword Attack (impeto, giganti)</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="15" customHeight="1" s="8">
       <c r="A142" s="12" t="inlineStr">
@@ -7405,7 +11364,41 @@
       </c>
       <c r="I142" s="12" t="inlineStr">
         <is>
-          <t>Baby</t>
+          <t>Baby Vegeta</t>
+        </is>
+      </c>
+      <c r="J142" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K142" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L142" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M142" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N142" s="7" t="inlineStr">
+        <is>
+          <t>Galick Gun (onda)</t>
+        </is>
+      </c>
+      <c r="O142" s="7" t="inlineStr">
+        <is>
+          <t>Finger Blitz Barrage (onda)</t>
+        </is>
+      </c>
+      <c r="P142" s="7" t="inlineStr">
+        <is>
+          <t>Final Flash (onda)</t>
+        </is>
+      </c>
+      <c r="Q142" s="7" t="inlineStr">
+        <is>
+          <t>Super Baby 1</t>
         </is>
       </c>
     </row>
@@ -7451,7 +11444,41 @@
       </c>
       <c r="I143" s="12" t="inlineStr">
         <is>
-          <t>Baby</t>
+          <t>Baby Vegeta</t>
+        </is>
+      </c>
+      <c r="J143" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K143" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L143" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M143" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N143" s="7" t="inlineStr">
+        <is>
+          <t>Galick Gun (onda)</t>
+        </is>
+      </c>
+      <c r="O143" s="7" t="inlineStr">
+        <is>
+          <t>Finger Blitz Barrage (onda)</t>
+        </is>
+      </c>
+      <c r="P143" s="7" t="inlineStr">
+        <is>
+          <t>Final Flash (onda)</t>
+        </is>
+      </c>
+      <c r="Q143" s="7" t="inlineStr">
+        <is>
+          <t>Super Baby 2</t>
         </is>
       </c>
     </row>
@@ -7497,7 +11524,41 @@
       </c>
       <c r="I144" s="12" t="inlineStr">
         <is>
-          <t>Baby</t>
+          <t>Baby Vegeta</t>
+        </is>
+      </c>
+      <c r="J144" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K144" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L144" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M144" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N144" s="7" t="inlineStr">
+        <is>
+          <t>Final Flash (onda)</t>
+        </is>
+      </c>
+      <c r="O144" s="7" t="inlineStr">
+        <is>
+          <t>Full Power Energy Blast Volley (onda)</t>
+        </is>
+      </c>
+      <c r="P144" s="7" t="inlineStr">
+        <is>
+          <t>Revenge Death Ball (onda)</t>
+        </is>
+      </c>
+      <c r="Q144" s="7" t="inlineStr">
+        <is>
+          <t>Baby Oozaru</t>
         </is>
       </c>
     </row>
@@ -7543,7 +11604,36 @@
       </c>
       <c r="I145" s="12" t="inlineStr">
         <is>
-          <t>Baby</t>
+          <t>Baby Vegeta</t>
+        </is>
+      </c>
+      <c r="J145" t="n">
+        <v>5</v>
+      </c>
+      <c r="K145" t="n">
+        <v>5</v>
+      </c>
+      <c r="L145" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
+      <c r="N145" s="7" t="inlineStr">
+        <is>
+          <t>Super Galick Gun (onda)</t>
+        </is>
+      </c>
+      <c r="O145" s="7" t="inlineStr">
+        <is>
+          <t>Gigantic Flame (onda)</t>
+        </is>
+      </c>
+      <c r="P145" s="7" t="inlineStr">
+        <is>
+          <t>Revenge Death Ball Final (onda)</t>
         </is>
       </c>
     </row>
@@ -7589,7 +11679,36 @@
       </c>
       <c r="I146" s="12" t="inlineStr">
         <is>
-          <t>C-17</t>
+          <t>Super C-17</t>
+        </is>
+      </c>
+      <c r="J146" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K146" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L146" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M146" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N146" s="7" t="inlineStr">
+        <is>
+          <t>Full Power Energy Wave (onda)</t>
+        </is>
+      </c>
+      <c r="O146" s="7" t="inlineStr">
+        <is>
+          <t>Hell's Storm (onda)</t>
+        </is>
+      </c>
+      <c r="P146" s="7" t="inlineStr">
+        <is>
+          <t>Shocking Death Ball (onda)</t>
         </is>
       </c>
     </row>
@@ -7638,6 +11757,35 @@
           <t>Su Shenron</t>
         </is>
       </c>
+      <c r="J147" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K147" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L147" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M147" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>Burst Attack (onda)</t>
+        </is>
+      </c>
+      <c r="O147" s="7" t="inlineStr">
+        <is>
+          <t>Burning Tornado (impeto)</t>
+        </is>
+      </c>
+      <c r="P147" s="7" t="inlineStr">
+        <is>
+          <t>Blaster Meteor (onda)</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="15" customHeight="1" s="8">
       <c r="A148" s="12" t="inlineStr">
@@ -7684,6 +11832,40 @@
           <t>Ii Shenron</t>
         </is>
       </c>
+      <c r="J148" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K148" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L148" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M148" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N148" s="7" t="inlineStr">
+        <is>
+          <t>Trap Shooter (onda)</t>
+        </is>
+      </c>
+      <c r="O148" s="7" t="inlineStr">
+        <is>
+          <t>Blazing Storm (onda)</t>
+        </is>
+      </c>
+      <c r="P148" s="7" t="inlineStr">
+        <is>
+          <t>Gigantic Blaze (onda)</t>
+        </is>
+      </c>
+      <c r="Q148" s="7" t="inlineStr">
+        <is>
+          <t>Super Ii Shenron</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="15" customHeight="1" s="8">
       <c r="A149" s="12" t="inlineStr">
@@ -7730,6 +11912,35 @@
           <t>Ii Shenron</t>
         </is>
       </c>
+      <c r="J149" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K149" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L149" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M149" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N149" s="7" t="inlineStr">
+        <is>
+          <t>Gigantic Blaze (onda)</t>
+        </is>
+      </c>
+      <c r="O149" s="7" t="inlineStr">
+        <is>
+          <t>Dragon Thunder (impeto)</t>
+        </is>
+      </c>
+      <c r="P149" s="7" t="inlineStr">
+        <is>
+          <t>Minus Energy Power Ball (onda)</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="15" customHeight="1" s="8">
       <c r="A150" s="12" t="inlineStr">
@@ -7776,6 +11987,35 @@
           <t>Son Gohan (nonno)</t>
         </is>
       </c>
+      <c r="J150" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K150" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L150" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M150" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N150" s="7" t="inlineStr">
+        <is>
+          <t>Kamehameha (onda)</t>
+        </is>
+      </c>
+      <c r="O150" s="7" t="inlineStr">
+        <is>
+          <t>Turtle School Four Virtues (impeto)</t>
+        </is>
+      </c>
+      <c r="P150" s="7" t="inlineStr">
+        <is>
+          <t>Turtle School Tranquility (impeto)</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="15" customHeight="1" s="8">
       <c r="A151" s="12" t="inlineStr">
@@ -7822,6 +12062,35 @@
           <t>Tao Pai Pai</t>
         </is>
       </c>
+      <c r="J151" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K151" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L151" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M151" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>The Original Dodon-Pa (onda)</t>
+        </is>
+      </c>
+      <c r="O151" s="7" t="inlineStr">
+        <is>
+          <t>Crane Style Assassin Strike (impeto)</t>
+        </is>
+      </c>
+      <c r="P151" s="7" t="inlineStr">
+        <is>
+          <t>Ultimate Final Plan (impeto)</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="15" customHeight="1" s="8">
       <c r="A152" s="12" t="inlineStr">
@@ -7865,7 +12134,36 @@
       </c>
       <c r="I152" s="12" t="inlineStr">
         <is>
-          <t>Tao Pai Pai</t>
+          <t>Tao Pai Pai (cyborg)</t>
+        </is>
+      </c>
+      <c r="J152" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K152" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L152" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M152" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N152" s="7" t="inlineStr">
+        <is>
+          <t>Dodon Ray (onda)</t>
+        </is>
+      </c>
+      <c r="O152" s="7" t="inlineStr">
+        <is>
+          <t>Hidden Blade (impeto)</t>
+        </is>
+      </c>
+      <c r="P152" s="7" t="inlineStr">
+        <is>
+          <t>Super Dodon Wave (onda)</t>
         </is>
       </c>
     </row>
@@ -7914,6 +12212,35 @@
           <t>Piccolo Daimao</t>
         </is>
       </c>
+      <c r="J153" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K153" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L153" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M153" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N153" s="7" t="inlineStr">
+        <is>
+          <t>Soumasen (onda)</t>
+        </is>
+      </c>
+      <c r="O153" s="7" t="inlineStr">
+        <is>
+          <t>Your name is Drum (impeto)</t>
+        </is>
+      </c>
+      <c r="P153" s="7" t="inlineStr">
+        <is>
+          <t>Explosive Demon Wave (onda)</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="15" customHeight="1" s="8">
       <c r="A154" s="12" t="inlineStr">
@@ -7960,6 +12287,35 @@
           <t>Tambourine</t>
         </is>
       </c>
+      <c r="J154" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K154" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L154" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M154" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N154" s="7" t="inlineStr">
+        <is>
+          <t>Chou Makouhou (onda)</t>
+        </is>
+      </c>
+      <c r="O154" s="7" t="inlineStr">
+        <is>
+          <t>Soumasen (onda)</t>
+        </is>
+      </c>
+      <c r="P154" s="7" t="inlineStr">
+        <is>
+          <t>Super Marengeki (impeto)</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="15" customHeight="1" s="8">
       <c r="A155" s="12" t="inlineStr">
@@ -8006,6 +12362,35 @@
           <t>C-8</t>
         </is>
       </c>
+      <c r="J155" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K155" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L155" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M155" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N155" s="7" t="inlineStr">
+        <is>
+          <t>Eighter Attack (impeto)</t>
+        </is>
+      </c>
+      <c r="O155" s="7" t="inlineStr">
+        <is>
+          <t>Eighter's Anger (onda)</t>
+        </is>
+      </c>
+      <c r="P155" s="7" t="inlineStr">
+        <is>
+          <t>You Hurt Goku! (impeto)</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="15" customHeight="1" s="8">
       <c r="A156" s="12" t="inlineStr">
@@ -8052,6 +12437,35 @@
           <t>Generale Blue</t>
         </is>
       </c>
+      <c r="J156" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K156" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L156" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M156" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N156" s="7" t="inlineStr">
+        <is>
+          <t>I'll Shoot You! (onda)</t>
+        </is>
+      </c>
+      <c r="O156" s="7" t="inlineStr">
+        <is>
+          <t>Skewer! (impeto)</t>
+        </is>
+      </c>
+      <c r="P156" s="7" t="inlineStr">
+        <is>
+          <t>Rocket Engine Spark (impeto)</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="15" customHeight="1" s="8">
       <c r="A157" s="12" t="inlineStr">
@@ -8098,6 +12512,35 @@
           <t>Namu</t>
         </is>
       </c>
+      <c r="J157" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K157" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L157" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M157" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N157" s="7" t="inlineStr">
+        <is>
+          <t>Shura Gekiretsuken (impeto)</t>
+        </is>
+      </c>
+      <c r="O157" s="7" t="inlineStr">
+        <is>
+          <t>Cross Arm Attack (impeto)</t>
+        </is>
+      </c>
+      <c r="P157" s="7" t="inlineStr">
+        <is>
+          <t>Cross Arm Dive (impeto)</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="15" customHeight="1" s="8">
       <c r="A158" s="12" t="inlineStr">
@@ -8144,6 +12587,35 @@
           <t>Akkuman</t>
         </is>
       </c>
+      <c r="J158" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K158" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L158" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M158" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N158" s="7" t="inlineStr">
+        <is>
+          <t>Fork Attack (onda)</t>
+        </is>
+      </c>
+      <c r="O158" s="7" t="inlineStr">
+        <is>
+          <t>Demon Fork Rush (impeto)</t>
+        </is>
+      </c>
+      <c r="P158" s="7" t="inlineStr">
+        <is>
+          <t>Devilmite Beam (onda)</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="15" customHeight="1" s="8">
       <c r="A159" s="12" t="inlineStr">
@@ -8187,7 +12659,36 @@
       </c>
       <c r="I159" s="12" t="inlineStr">
         <is>
-          <t>Chichi</t>
+          <t>Chichi (bambina)</t>
+        </is>
+      </c>
+      <c r="J159" t="n">
+        <v>3</v>
+      </c>
+      <c r="K159" t="n">
+        <v>2</v>
+      </c>
+      <c r="L159" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M159" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N159" s="7" t="inlineStr">
+        <is>
+          <t>Stay Away From Me! (impeto)</t>
+        </is>
+      </c>
+      <c r="O159" s="7" t="inlineStr">
+        <is>
+          <t>That Won't Work (onda)</t>
+        </is>
+      </c>
+      <c r="P159" s="7" t="inlineStr">
+        <is>
+          <t>Save Goku! (impeto)</t>
         </is>
       </c>
     </row>
@@ -8236,6 +12737,40 @@
           <t>Robot di Pilaf</t>
         </is>
       </c>
+      <c r="J160" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K160" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L160" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M160" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N160" s="7" t="inlineStr">
+        <is>
+          <t>Gigant Rock Throw (onda)</t>
+        </is>
+      </c>
+      <c r="O160" s="7" t="inlineStr">
+        <is>
+          <t>Rolling Smash (impeto)</t>
+        </is>
+      </c>
+      <c r="P160" s="7" t="inlineStr">
+        <is>
+          <t>Great Pilaf Operation (impeto)</t>
+        </is>
+      </c>
+      <c r="Q160" s="7" t="inlineStr">
+        <is>
+          <t>Robot di Pilaf (combinato)</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="15" customHeight="1" s="8">
       <c r="A161" s="12" t="inlineStr">
@@ -8282,6 +12817,35 @@
           <t>Robot di Pilaf</t>
         </is>
       </c>
+      <c r="J161" t="n">
+        <v>5</v>
+      </c>
+      <c r="K161" t="n">
+        <v>5</v>
+      </c>
+      <c r="L161" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>Double Buster (onda)</t>
+        </is>
+      </c>
+      <c r="O161" s="7" t="inlineStr">
+        <is>
+          <t>Gatling Gun (impeto)</t>
+        </is>
+      </c>
+      <c r="P161" s="7" t="inlineStr">
+        <is>
+          <t>Launch Missiles! (onda)</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="15" customHeight="1" s="8">
       <c r="A162" s="12" t="inlineStr">
@@ -8300,7 +12864,7 @@
       </c>
       <c r="D162" s="12" t="inlineStr">
         <is>
-          <t>SS+</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="E162" s="12" t="inlineStr">
@@ -8326,6 +12890,35 @@
       <c r="I162" s="12" t="inlineStr">
         <is>
           <t>Arale</t>
+        </is>
+      </c>
+      <c r="J162" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K162" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L162" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M162" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>Woohoo! (onda)</t>
+        </is>
+      </c>
+      <c r="O162" s="7" t="inlineStr">
+        <is>
+          <t>Ping! (impeto, giganti)</t>
+        </is>
+      </c>
+      <c r="P162" s="7" t="inlineStr">
+        <is>
+          <t>Playing Pro-Wrestling (impeto, giganti)</t>
         </is>
       </c>
     </row>
@@ -8520,7 +13113,7 @@
       </c>
       <c r="I167" s="12" t="inlineStr">
         <is>
-          <t>Chichi</t>
+          <t>Chichi (adulta)</t>
         </is>
       </c>
     </row>
@@ -8863,7 +13456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="110" customWidth="1" style="7" min="1" max="1"/>
@@ -8949,7 +13542,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Colonna 'persona' (spec 031, D-048): lo stesso valore per le forme della stessa persona (es. «Son Goku» per tutte le forme di Goku). L'app la usa per non dare missioni «Vai da», «Batti» e «Porta» verso un'altra forma di chi le dà, e per non proporre due forme della stessa persona come starter a caso. Vuota: il personaggio è una persona a sé.</t>
+          <t>Colonna 'persona' (spec 039, D-064, cambia D-048): una persona è uno stesso personaggio con le sue trasformazioni, e il valore è il nome della sua prima forma (es. «Son Goku (metà)» per Goku (metà) e Goku (metà) SSJ; Goku (inizio), (metà) e (fine) sono tre persone). In una partita una persona sta in un solo posto. L'app la usa anche per non dare missioni «Vai da», «Batti» e «Porta» verso un'altra forma di chi le dà, e per non proporre due forme della stessa persona come starter a caso.</t>
         </is>
       </c>
     </row>
@@ -8959,6 +13552,9 @@
           <t>Colonne della scheda di combattimento (spec 037, D-059), tutte facoltative: vuote valgono come la scheda normale. barre: da 3 a 5 (normale 4). potenza e velocità: da 1 a 5, potenza + velocità = 6 (normale 3 e 3). gigante: «sì» se gli impeti non lo colpiscono. mossa 1, mossa 2, mossa finale: nome e tipo, es. «Kamehameha (onda)», «Meteor Smash (impeto)»; «(impeto, giganti)» per un impeto che colpisce anche i giganti, come Penetrate!. Le mosse sono quelle di BT3 (due Blast 2 e la Ultimate), con i nomi inglesi del gioco: l'energia è un'onda, il fisico un impeto (D-057). si trasforma in: il nome della forma successiva, un personaggio di questa lista con un tier.</t>
         </is>
       </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>

--- a/docs/personaggi-bt3.xlsx
+++ b/docs/personaggi-bt3.xlsx
@@ -13172,7 +13172,7 @@
         </is>
       </c>
       <c r="B2" s="14" t="n">
-        <v>6000</v>
+        <v>3900</v>
       </c>
       <c r="C2" s="12" t="inlineStr">
         <is>
@@ -13187,7 +13187,7 @@
         </is>
       </c>
       <c r="B3" s="14" t="n">
-        <v>5500</v>
+        <v>3600</v>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
@@ -13202,7 +13202,7 @@
         </is>
       </c>
       <c r="B4" s="14" t="n">
-        <v>5000</v>
+        <v>3200</v>
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
@@ -13217,7 +13217,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>4200</v>
+        <v>2700</v>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         </is>
       </c>
       <c r="B6" s="14" t="n">
-        <v>3800</v>
+        <v>2500</v>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
@@ -13247,7 +13247,7 @@
         </is>
       </c>
       <c r="B7" s="14" t="n">
-        <v>3400</v>
+        <v>2200</v>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>2800</v>
+        <v>1800</v>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
@@ -13277,7 +13277,7 @@
         </is>
       </c>
       <c r="B9" s="14" t="n">
-        <v>2500</v>
+        <v>1600</v>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         </is>
       </c>
       <c r="B10" s="14" t="n">
-        <v>2200</v>
+        <v>1400</v>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
@@ -13307,7 +13307,7 @@
         </is>
       </c>
       <c r="B11" s="14" t="n">
-        <v>1900</v>
+        <v>1200</v>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
@@ -13322,7 +13322,7 @@
         </is>
       </c>
       <c r="B12" s="14" t="n">
-        <v>1700</v>
+        <v>1100</v>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
@@ -13337,7 +13337,7 @@
         </is>
       </c>
       <c r="B13" s="14" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>

--- a/docs/personaggi-bt3.xlsx
+++ b/docs/personaggi-bt3.xlsx
@@ -12,7 +12,7 @@
     <sheet name="leggimi" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'personaggi'!$A$1:$Q$167</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'personaggi'!$A$1:$R$167</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Q167"/>
+  <dimension ref="A1:R167"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="36" customWidth="1" style="7" min="1" max="1"/>
@@ -463,6 +463,7 @@
     <col width="34" customWidth="1" style="8" min="15" max="15"/>
     <col width="36" customWidth="1" style="8" min="16" max="16"/>
     <col width="30" customWidth="1" style="8" min="17" max="17"/>
+    <col width="20" customWidth="1" style="8" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="8">
@@ -551,6 +552,11 @@
           <t>si trasforma in</t>
         </is>
       </c>
+      <c r="R1" s="10" t="inlineStr">
+        <is>
+          <t>cura trasformandosi</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="8">
       <c r="A2" s="12" t="inlineStr">
@@ -706,6 +712,7 @@
           <t>Son Goku (metà) SSJ</t>
         </is>
       </c>
+      <c r="R3" s="7" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1" s="8">
       <c r="A4" s="12" t="inlineStr">
@@ -861,6 +868,7 @@
           <t>Son Goku (fine) SSJ</t>
         </is>
       </c>
+      <c r="R5" s="7" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1" s="8">
       <c r="A6" s="12" t="inlineStr">
@@ -921,7 +929,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N6" s="7" t="inlineStr">
         <is>
           <t>Super Kamehameha (onda)</t>
         </is>
@@ -941,6 +949,7 @@
           <t>Son Goku (fine) SSJ2</t>
         </is>
       </c>
+      <c r="R6" s="7" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1" s="8">
       <c r="A7" s="12" t="inlineStr">
@@ -1021,6 +1030,7 @@
           <t>Son Goku (fine) SSJ3</t>
         </is>
       </c>
+      <c r="R7" s="7" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1" s="8">
       <c r="A8" s="12" t="inlineStr">
@@ -1091,7 +1101,7 @@
           <t>Super Explosive Wave (onda)</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P8" s="7" t="inlineStr">
         <is>
           <t>Dragon Fist (impeto, giganti)</t>
         </is>
@@ -1161,7 +1171,7 @@
           <t>Kamehameha (onda)</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O9" s="7" t="inlineStr">
         <is>
           <t>Dragon Fist (impeto, giganti)</t>
         </is>
@@ -1176,6 +1186,7 @@
           <t>Son Goku (GT) SSJ</t>
         </is>
       </c>
+      <c r="R9" s="7" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1" s="8">
       <c r="A10" s="12" t="inlineStr">
@@ -1236,7 +1247,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N10" s="7" t="inlineStr">
         <is>
           <t>Super Kamehameha (onda)</t>
         </is>
@@ -1256,6 +1267,7 @@
           <t>Son Goku (GT) SSJ3</t>
         </is>
       </c>
+      <c r="R10" s="7" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1" s="8">
       <c r="A11" s="12" t="inlineStr">
@@ -1326,7 +1338,7 @@
           <t>Full Power Energy Blast Volley (onda)</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P11" s="7" t="inlineStr">
         <is>
           <t>Dragon Fist (impeto, giganti)</t>
         </is>
@@ -1336,6 +1348,7 @@
           <t>Son Goku SSJ4</t>
         </is>
       </c>
+      <c r="R11" s="7" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1" s="8">
       <c r="A12" s="12" t="inlineStr">
@@ -1406,7 +1419,7 @@
           <t>Meteor Crash (impeto)</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P12" s="7" t="inlineStr">
         <is>
           <t>Dragon Fist (impeto, giganti)</t>
         </is>
@@ -1486,11 +1499,12 @@
           <t>Penetrate! (impeto, giganti)</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Q13" s="7" t="inlineStr">
         <is>
           <t>Son Goku (bambino) Oozaru</t>
         </is>
       </c>
+      <c r="R13" s="7" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1" s="8">
       <c r="A14" s="12" t="inlineStr">
@@ -1537,16 +1551,16 @@
           <t>Son Goku (bambino)</t>
         </is>
       </c>
-      <c r="J14" t="n">
+      <c r="J14" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K14" s="7" t="n">
         <v>5</v>
       </c>
       <c r="L14" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M14" s="7" t="inlineStr">
         <is>
           <t>sì</t>
         </is>
@@ -1556,7 +1570,7 @@
           <t>Chou Makouhou (onda)</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="O14" s="7" t="inlineStr">
         <is>
           <t>Gigant Rock Throw (onda)</t>
         </is>
@@ -1612,10 +1626,10 @@
           <t>Son Gohan (bambino)</t>
         </is>
       </c>
-      <c r="J15" t="n">
-        <v>3</v>
-      </c>
-      <c r="K15" t="n">
+      <c r="J15" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" s="7" t="n">
         <v>2</v>
       </c>
       <c r="L15" s="7" t="n">
@@ -1721,6 +1735,7 @@
           <t>Son Gohan (ragazzo) SSJ</t>
         </is>
       </c>
+      <c r="R16" s="7" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1" s="8">
       <c r="A17" s="12" t="inlineStr">
@@ -1801,6 +1816,7 @@
           <t>Son Gohan (ragazzo) SSJ2</t>
         </is>
       </c>
+      <c r="R17" s="7" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1" s="8">
       <c r="A18" s="12" t="inlineStr">
@@ -1956,6 +1972,7 @@
           <t>Son Gohan SSJ</t>
         </is>
       </c>
+      <c r="R19" s="7" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1" s="8">
       <c r="A20" s="12" t="inlineStr">
@@ -2036,6 +2053,7 @@
           <t>Son Gohan SSJ2</t>
         </is>
       </c>
+      <c r="R20" s="7" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1" s="8">
       <c r="A21" s="12" t="inlineStr">
@@ -2341,6 +2359,7 @@
           <t>Son Gohan (futuro) SSJ</t>
         </is>
       </c>
+      <c r="R24" s="7" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1" s="8">
       <c r="A25" s="12" t="inlineStr">
@@ -2462,10 +2481,10 @@
           <t>Son Goten</t>
         </is>
       </c>
-      <c r="J26" t="n">
-        <v>3</v>
-      </c>
-      <c r="K26" t="n">
+      <c r="J26" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" s="7" t="n">
         <v>2</v>
       </c>
       <c r="L26" s="7" t="n">
@@ -2496,6 +2515,7 @@
           <t>Son Goten SSJ</t>
         </is>
       </c>
+      <c r="R26" s="7" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1" s="8">
       <c r="A27" s="12" t="inlineStr">
@@ -2651,6 +2671,7 @@
           <t>Vegeta (scouter) Oozaru</t>
         </is>
       </c>
+      <c r="R28" s="7" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1" s="8">
       <c r="A29" s="12" t="inlineStr">
@@ -2806,6 +2827,7 @@
           <t>Vegeta SSJ</t>
         </is>
       </c>
+      <c r="R30" s="7" t="n"/>
     </row>
     <row r="31" ht="15" customHeight="1" s="8">
       <c r="A31" s="12" t="inlineStr">
@@ -2886,6 +2908,7 @@
           <t>Super Vegeta</t>
         </is>
       </c>
+      <c r="R31" s="7" t="n"/>
     </row>
     <row r="32" ht="15" customHeight="1" s="8">
       <c r="A32" s="12" t="inlineStr">
@@ -3041,6 +3064,7 @@
           <t>Vegeta (seconda forma) SSJ</t>
         </is>
       </c>
+      <c r="R33" s="7" t="n"/>
     </row>
     <row r="34" ht="15" customHeight="1" s="8">
       <c r="A34" s="12" t="inlineStr">
@@ -3121,6 +3145,7 @@
           <t>Vegeta (seconda forma) SSJ2</t>
         </is>
       </c>
+      <c r="R34" s="7" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1" s="8">
       <c r="A35" s="12" t="inlineStr">
@@ -3426,6 +3451,7 @@
           <t>Trunks (spada) SSJ</t>
         </is>
       </c>
+      <c r="R38" s="7" t="n"/>
     </row>
     <row r="39" ht="15" customHeight="1" s="8">
       <c r="A39" s="12" t="inlineStr">
@@ -3581,6 +3607,7 @@
           <t>Trunks SSJ</t>
         </is>
       </c>
+      <c r="R40" s="7" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1" s="8">
       <c r="A41" s="12" t="inlineStr">
@@ -3651,7 +3678,7 @@
           <t>Burning Breaker (impeto)</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="P41" s="7" t="inlineStr">
         <is>
           <t>Heat Dome Attack (impeto, giganti)</t>
         </is>
@@ -3661,6 +3688,7 @@
           <t>Super Trunks</t>
         </is>
       </c>
+      <c r="R41" s="7" t="n"/>
     </row>
     <row r="42" ht="15" customHeight="1" s="8">
       <c r="A42" s="12" t="inlineStr">
@@ -3710,7 +3738,7 @@
       <c r="J42" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="K42" t="n">
+      <c r="K42" s="7" t="n">
         <v>4</v>
       </c>
       <c r="L42" s="7" t="n">
@@ -3782,10 +3810,10 @@
           <t>Trunks (bambino)</t>
         </is>
       </c>
-      <c r="J43" t="n">
-        <v>3</v>
-      </c>
-      <c r="K43" t="n">
+      <c r="J43" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K43" s="7" t="n">
         <v>2</v>
       </c>
       <c r="L43" s="7" t="n">
@@ -3816,6 +3844,7 @@
           <t>Trunks (bambino) SSJ</t>
         </is>
       </c>
+      <c r="R43" s="7" t="n"/>
     </row>
     <row r="44" ht="15" customHeight="1" s="8">
       <c r="A44" s="12" t="inlineStr">
@@ -3862,10 +3891,10 @@
           <t>Trunks (bambino)</t>
         </is>
       </c>
-      <c r="J44" t="n">
-        <v>3</v>
-      </c>
-      <c r="K44" t="n">
+      <c r="J44" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K44" s="7" t="n">
         <v>2</v>
       </c>
       <c r="L44" s="7" t="n">
@@ -3971,6 +4000,7 @@
           <t>Gotenks SSJ</t>
         </is>
       </c>
+      <c r="R45" s="7" t="n"/>
     </row>
     <row r="46" ht="15" customHeight="1" s="8">
       <c r="A46" s="12" t="inlineStr">
@@ -4051,6 +4081,7 @@
           <t>Gotenks SSJ3</t>
         </is>
       </c>
+      <c r="R46" s="7" t="n"/>
     </row>
     <row r="47" ht="15" customHeight="1" s="8">
       <c r="A47" s="12" t="inlineStr">
@@ -4172,7 +4203,7 @@
           <t>Vegetto</t>
         </is>
       </c>
-      <c r="J48" t="n">
+      <c r="J48" s="7" t="n">
         <v>5</v>
       </c>
       <c r="K48" s="7" t="n">
@@ -4206,6 +4237,7 @@
           <t>Super Vegetto</t>
         </is>
       </c>
+      <c r="R48" s="7" t="n"/>
     </row>
     <row r="49" ht="15" customHeight="1" s="8">
       <c r="A49" s="12" t="inlineStr">
@@ -4252,7 +4284,7 @@
           <t>Vegetto</t>
         </is>
       </c>
-      <c r="J49" t="n">
+      <c r="J49" s="7" t="n">
         <v>5</v>
       </c>
       <c r="K49" s="7" t="n">
@@ -4327,7 +4359,7 @@
           <t>Super Gogeta</t>
         </is>
       </c>
-      <c r="J50" t="n">
+      <c r="J50" s="7" t="n">
         <v>5</v>
       </c>
       <c r="K50" s="7" t="n">
@@ -4852,10 +4884,10 @@
           <t>Jiaozi</t>
         </is>
       </c>
-      <c r="J57" t="n">
-        <v>3</v>
-      </c>
-      <c r="K57" t="n">
+      <c r="J57" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K57" s="7" t="n">
         <v>2</v>
       </c>
       <c r="L57" s="7" t="n">
@@ -4866,7 +4898,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="N57" s="7" t="inlineStr">
         <is>
           <t>Dodon Ray (onda)</t>
         </is>
@@ -4951,7 +4983,7 @@
           <t>Flash and Kill (impeto)</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="P58" s="7" t="inlineStr">
         <is>
           <t>Miracle Ka-Blam Slash (impeto, giganti)</t>
         </is>
@@ -5036,6 +5068,7 @@
           <t>Muten Roshi (massima potenza)</t>
         </is>
       </c>
+      <c r="R59" s="7" t="n"/>
     </row>
     <row r="60" ht="15" customHeight="1" s="8">
       <c r="A60" s="12" t="inlineStr">
@@ -5191,6 +5224,7 @@
           <t>Great Saiyaman 2-go</t>
         </is>
       </c>
+      <c r="R61" s="7" t="n"/>
     </row>
     <row r="62" ht="15" customHeight="1" s="8">
       <c r="A62" s="12" t="inlineStr">
@@ -5421,6 +5455,7 @@
           <t>Kibitoshin</t>
         </is>
       </c>
+      <c r="R64" s="7" t="n"/>
     </row>
     <row r="65" ht="15" customHeight="1" s="8">
       <c r="A65" s="12" t="inlineStr">
@@ -5576,6 +5611,7 @@
           <t>Super Uub</t>
         </is>
       </c>
+      <c r="R66" s="7" t="n"/>
     </row>
     <row r="67" ht="15" customHeight="1" s="8">
       <c r="A67" s="12" t="inlineStr">
@@ -5697,10 +5733,10 @@
           <t>Pan</t>
         </is>
       </c>
-      <c r="J68" t="n">
-        <v>3</v>
-      </c>
-      <c r="K68" t="n">
+      <c r="J68" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K68" s="7" t="n">
         <v>2</v>
       </c>
       <c r="L68" s="7" t="n">
@@ -5881,6 +5917,7 @@
           <t>Bardock Oozaru</t>
         </is>
       </c>
+      <c r="R70" s="7" t="n"/>
     </row>
     <row r="71" ht="15" customHeight="1" s="8">
       <c r="A71" s="12" t="inlineStr">
@@ -5927,16 +5964,16 @@
           <t>Bardock</t>
         </is>
       </c>
-      <c r="J71" t="n">
+      <c r="J71" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="K71" t="n">
+      <c r="K71" s="7" t="n">
         <v>5</v>
       </c>
       <c r="L71" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="M71" s="7" t="inlineStr">
         <is>
           <t>sì</t>
         </is>
@@ -6036,6 +6073,7 @@
           <t>Selypa Oozaru</t>
         </is>
       </c>
+      <c r="R72" s="7" t="n"/>
     </row>
     <row r="73" ht="15" customHeight="1" s="8">
       <c r="A73" s="12" t="inlineStr">
@@ -6082,21 +6120,21 @@
           <t>Selypa</t>
         </is>
       </c>
-      <c r="J73" t="n">
+      <c r="J73" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="K73" t="n">
+      <c r="K73" s="7" t="n">
         <v>5</v>
       </c>
       <c r="L73" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="M73" t="inlineStr">
+      <c r="M73" s="7" t="inlineStr">
         <is>
           <t>sì</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr">
+      <c r="N73" s="7" t="inlineStr">
         <is>
           <t>Chou Makouhou Barrage (impeto)</t>
         </is>
@@ -6191,6 +6229,7 @@
           <t>Re Vegeta Oozaru</t>
         </is>
       </c>
+      <c r="R74" s="7" t="n"/>
     </row>
     <row r="75" ht="15" customHeight="1" s="8">
       <c r="A75" s="12" t="inlineStr">
@@ -6237,16 +6276,16 @@
           <t>Re Vegeta</t>
         </is>
       </c>
-      <c r="J75" t="n">
+      <c r="J75" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="K75" t="n">
+      <c r="K75" s="7" t="n">
         <v>5</v>
       </c>
       <c r="L75" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="M75" s="7" t="inlineStr">
         <is>
           <t>sì</t>
         </is>
@@ -6346,6 +6385,7 @@
           <t>Raditz Oozaru</t>
         </is>
       </c>
+      <c r="R76" s="7" t="n"/>
     </row>
     <row r="77" ht="15" customHeight="1" s="8">
       <c r="A77" s="12" t="inlineStr">
@@ -6392,16 +6432,16 @@
           <t>Raditz</t>
         </is>
       </c>
-      <c r="J77" t="n">
+      <c r="J77" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="K77" t="n">
+      <c r="K77" s="7" t="n">
         <v>5</v>
       </c>
       <c r="L77" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="M77" t="inlineStr">
+      <c r="M77" s="7" t="inlineStr">
         <is>
           <t>sì</t>
         </is>
@@ -6481,7 +6521,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr">
+      <c r="N78" s="7" t="inlineStr">
         <is>
           <t>Volcano Explosion (onda)</t>
         </is>
@@ -6501,6 +6541,7 @@
           <t>Nappa Oozaru</t>
         </is>
       </c>
+      <c r="R78" s="7" t="n"/>
     </row>
     <row r="79" ht="15" customHeight="1" s="8">
       <c r="A79" s="12" t="inlineStr">
@@ -6547,16 +6588,16 @@
           <t>Nappa</t>
         </is>
       </c>
-      <c r="J79" t="n">
+      <c r="J79" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="K79" t="n">
+      <c r="K79" s="7" t="n">
         <v>5</v>
       </c>
       <c r="L79" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="M79" t="inlineStr">
+      <c r="M79" s="7" t="inlineStr">
         <is>
           <t>sì</t>
         </is>
@@ -6731,6 +6772,7 @@
           <t>Zarbon (trasformato)</t>
         </is>
       </c>
+      <c r="R81" s="7" t="n"/>
     </row>
     <row r="82" ht="15" customHeight="1" s="8">
       <c r="A82" s="12" t="inlineStr">
@@ -6941,7 +6983,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr">
+      <c r="N84" s="7" t="inlineStr">
         <is>
           <t>Full Power Energy Wave (onda)</t>
         </is>
@@ -7176,7 +7218,7 @@
           <t>Galaxy Dynamite (onda)</t>
         </is>
       </c>
-      <c r="P87" t="inlineStr">
+      <c r="P87" s="7" t="inlineStr">
         <is>
           <t>Body Change (impeto, giganti)</t>
         </is>
@@ -7452,10 +7494,10 @@
           <t>Guldo</t>
         </is>
       </c>
-      <c r="J91" t="n">
-        <v>3</v>
-      </c>
-      <c r="K91" t="n">
+      <c r="J91" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K91" s="7" t="n">
         <v>2</v>
       </c>
       <c r="L91" s="7" t="n">
@@ -7561,6 +7603,7 @@
           <t>Freeza (seconda forma)</t>
         </is>
       </c>
+      <c r="R92" s="7" t="n"/>
     </row>
     <row r="93" ht="15" customHeight="1" s="8">
       <c r="A93" s="12" t="inlineStr">
@@ -7641,6 +7684,7 @@
           <t>Freeza (terza forma)</t>
         </is>
       </c>
+      <c r="R93" s="7" t="n"/>
     </row>
     <row r="94" ht="15" customHeight="1" s="8">
       <c r="A94" s="12" t="inlineStr">
@@ -7721,6 +7765,7 @@
           <t>Freeza (forma finale)</t>
         </is>
       </c>
+      <c r="R94" s="7" t="n"/>
     </row>
     <row r="95" ht="15" customHeight="1" s="8">
       <c r="A95" s="12" t="inlineStr">
@@ -7801,6 +7846,7 @@
           <t>Freeza (massima potenza)</t>
         </is>
       </c>
+      <c r="R95" s="7" t="n"/>
     </row>
     <row r="96" ht="15" customHeight="1" s="8">
       <c r="A96" s="12" t="inlineStr">
@@ -8323,7 +8369,7 @@
       </c>
       <c r="P102" s="7" t="inlineStr">
         <is>
-          <t>Drain Life 19 (impeto)</t>
+          <t>Drain Life 19 (impeto, risucchio)</t>
         </is>
       </c>
     </row>
@@ -8398,7 +8444,7 @@
       </c>
       <c r="P103" s="7" t="inlineStr">
         <is>
-          <t>Drain Life 20 (impeto)</t>
+          <t>Drain Life 20 (impeto, risucchio)</t>
         </is>
       </c>
     </row>
@@ -8473,7 +8519,7 @@
       </c>
       <c r="P104" s="7" t="inlineStr">
         <is>
-          <t>Drain Life Cell (impeto)</t>
+          <t>Drain Life Cell (impeto, risucchio)</t>
         </is>
       </c>
       <c r="Q104" s="7" t="inlineStr">
@@ -8481,6 +8527,7 @@
           <t>Cell (seconda forma)</t>
         </is>
       </c>
+      <c r="R104" s="7" t="n"/>
     </row>
     <row r="105" ht="15" customHeight="1" s="8">
       <c r="A105" s="12" t="inlineStr">
@@ -8548,7 +8595,7 @@
       </c>
       <c r="O105" s="7" t="inlineStr">
         <is>
-          <t>Drain Life Cell (impeto)</t>
+          <t>Drain Life Cell (impeto, risucchio)</t>
         </is>
       </c>
       <c r="P105" s="7" t="inlineStr">
@@ -8560,6 +8607,9 @@
         <is>
           <t>Cell (forma perfetta)</t>
         </is>
+      </c>
+      <c r="R105" s="7" t="n">
+        <v>2500</v>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1" s="8">
@@ -8641,6 +8691,9 @@
           <t>Cell (perfetto, massima potenza)</t>
         </is>
       </c>
+      <c r="R106" s="7" t="n">
+        <v>2500</v>
+      </c>
     </row>
     <row r="107" ht="15" customHeight="1" s="8">
       <c r="A107" s="12" t="inlineStr">
@@ -9021,6 +9074,7 @@
           <t>Super Buu (Gotenks assorbito)</t>
         </is>
       </c>
+      <c r="R111" s="7" t="n"/>
     </row>
     <row r="112" ht="15" customHeight="1" s="8">
       <c r="A112" s="12" t="inlineStr">
@@ -9101,6 +9155,7 @@
           <t>Super Buu (Son Gohan assorbito)</t>
         </is>
       </c>
+      <c r="R112" s="7" t="n"/>
     </row>
     <row r="113" ht="15" customHeight="1" s="8">
       <c r="A113" s="12" t="inlineStr">
@@ -9372,10 +9427,10 @@
           <t>Bobbidi</t>
         </is>
       </c>
-      <c r="J116" t="n">
-        <v>3</v>
-      </c>
-      <c r="K116" t="n">
+      <c r="J116" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K116" s="7" t="n">
         <v>2</v>
       </c>
       <c r="L116" s="7" t="n">
@@ -9631,6 +9686,7 @@
           <t>Super Garlic Jr.</t>
         </is>
       </c>
+      <c r="R119" s="7" t="n"/>
     </row>
     <row r="120" ht="15" customHeight="1" s="8">
       <c r="A120" s="12" t="inlineStr">
@@ -9686,7 +9742,7 @@
       <c r="L120" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="M120" t="inlineStr">
+      <c r="M120" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9861,6 +9917,7 @@
           <t>Turles Oozaru</t>
         </is>
       </c>
+      <c r="R122" s="7" t="n"/>
     </row>
     <row r="123" ht="15" customHeight="1" s="8">
       <c r="A123" s="12" t="inlineStr">
@@ -9907,16 +9964,16 @@
           <t>Turles</t>
         </is>
       </c>
-      <c r="J123" t="n">
+      <c r="J123" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="K123" t="n">
+      <c r="K123" s="7" t="n">
         <v>5</v>
       </c>
       <c r="L123" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="M123" t="inlineStr">
+      <c r="M123" s="7" t="inlineStr">
         <is>
           <t>sì</t>
         </is>
@@ -10016,6 +10073,7 @@
           <t>Slug (gigante)</t>
         </is>
       </c>
+      <c r="R124" s="7" t="n"/>
     </row>
     <row r="125" ht="15" customHeight="1" s="8">
       <c r="A125" s="12" t="inlineStr">
@@ -10062,16 +10120,16 @@
           <t>Slug</t>
         </is>
       </c>
-      <c r="J125" t="n">
+      <c r="J125" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="K125" t="n">
+      <c r="K125" s="7" t="n">
         <v>5</v>
       </c>
       <c r="L125" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="M125" t="inlineStr">
+      <c r="M125" s="7" t="inlineStr">
         <is>
           <t>sì</t>
         </is>
@@ -10246,6 +10304,7 @@
           <t>Cooler (forma finale)</t>
         </is>
       </c>
+      <c r="R127" s="7" t="n"/>
     </row>
     <row r="128" ht="15" customHeight="1" s="8">
       <c r="A128" s="12" t="inlineStr">
@@ -10476,6 +10535,7 @@
           <t>Super C-13</t>
         </is>
       </c>
+      <c r="R130" s="7" t="n"/>
     </row>
     <row r="131" ht="15" customHeight="1" s="8">
       <c r="A131" s="12" t="inlineStr">
@@ -10597,7 +10657,7 @@
           <t>Broli</t>
         </is>
       </c>
-      <c r="J132" t="n">
+      <c r="J132" s="7" t="n">
         <v>5</v>
       </c>
       <c r="K132" s="7" t="n">
@@ -10631,6 +10691,7 @@
           <t>Broli SSJ</t>
         </is>
       </c>
+      <c r="R132" s="7" t="n"/>
     </row>
     <row r="133" ht="15" customHeight="1" s="8">
       <c r="A133" s="12" t="inlineStr">
@@ -10677,7 +10738,7 @@
           <t>Broli</t>
         </is>
       </c>
-      <c r="J133" t="n">
+      <c r="J133" s="7" t="n">
         <v>5</v>
       </c>
       <c r="K133" s="7" t="n">
@@ -10711,6 +10772,7 @@
           <t>Broli Super Saiyan Leggendario</t>
         </is>
       </c>
+      <c r="R133" s="7" t="n"/>
     </row>
     <row r="134" ht="15" customHeight="1" s="8">
       <c r="A134" s="12" t="inlineStr">
@@ -10846,7 +10908,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N135" t="inlineStr">
+      <c r="N135" s="7" t="inlineStr">
         <is>
           <t>Shoot Blaster (onda)</t>
         </is>
@@ -10941,6 +11003,7 @@
           <t>Bojack (massima potenza)</t>
         </is>
       </c>
+      <c r="R136" s="7" t="n"/>
     </row>
     <row r="137" ht="15" customHeight="1" s="8">
       <c r="A137" s="12" t="inlineStr">
@@ -11096,6 +11159,7 @@
           <t>Super Janemba</t>
         </is>
       </c>
+      <c r="R138" s="7" t="n"/>
     </row>
     <row r="139" ht="15" customHeight="1" s="8">
       <c r="A139" s="12" t="inlineStr">
@@ -11156,7 +11220,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N139" t="inlineStr">
+      <c r="N139" s="7" t="inlineStr">
         <is>
           <t>Chou Makouhou (onda)</t>
         </is>
@@ -11316,7 +11380,7 @@
           <t>Brave Slash (onda)</t>
         </is>
       </c>
-      <c r="P141" t="inlineStr">
+      <c r="P141" s="7" t="inlineStr">
         <is>
           <t>Brave Sword Attack (impeto, giganti)</t>
         </is>
@@ -11401,6 +11465,7 @@
           <t>Super Baby 1</t>
         </is>
       </c>
+      <c r="R142" s="7" t="n"/>
     </row>
     <row r="143" ht="15" customHeight="1" s="8">
       <c r="A143" s="12" t="inlineStr">
@@ -11481,6 +11546,7 @@
           <t>Super Baby 2</t>
         </is>
       </c>
+      <c r="R143" s="7" t="n"/>
     </row>
     <row r="144" ht="15" customHeight="1" s="8">
       <c r="A144" s="12" t="inlineStr">
@@ -11561,6 +11627,7 @@
           <t>Baby Oozaru</t>
         </is>
       </c>
+      <c r="R144" s="7" t="n"/>
     </row>
     <row r="145" ht="15" customHeight="1" s="8">
       <c r="A145" s="12" t="inlineStr">
@@ -11607,16 +11674,16 @@
           <t>Baby Vegeta</t>
         </is>
       </c>
-      <c r="J145" t="n">
+      <c r="J145" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="K145" t="n">
+      <c r="K145" s="7" t="n">
         <v>5</v>
       </c>
       <c r="L145" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="M145" t="inlineStr">
+      <c r="M145" s="7" t="inlineStr">
         <is>
           <t>sì</t>
         </is>
@@ -11771,7 +11838,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N147" t="inlineStr">
+      <c r="N147" s="7" t="inlineStr">
         <is>
           <t>Burst Attack (onda)</t>
         </is>
@@ -11866,6 +11933,7 @@
           <t>Super Ii Shenron</t>
         </is>
       </c>
+      <c r="R148" s="7" t="n"/>
     </row>
     <row r="149" ht="15" customHeight="1" s="8">
       <c r="A149" s="12" t="inlineStr">
@@ -12076,7 +12144,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N151" t="inlineStr">
+      <c r="N151" s="7" t="inlineStr">
         <is>
           <t>The Original Dodon-Pa (onda)</t>
         </is>
@@ -12662,10 +12730,10 @@
           <t>Chichi (bambina)</t>
         </is>
       </c>
-      <c r="J159" t="n">
-        <v>3</v>
-      </c>
-      <c r="K159" t="n">
+      <c r="J159" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K159" s="7" t="n">
         <v>2</v>
       </c>
       <c r="L159" s="7" t="n">
@@ -12771,6 +12839,7 @@
           <t>Robot di Pilaf (combinato)</t>
         </is>
       </c>
+      <c r="R160" s="7" t="n"/>
     </row>
     <row r="161" ht="15" customHeight="1" s="8">
       <c r="A161" s="12" t="inlineStr">
@@ -12817,21 +12886,21 @@
           <t>Robot di Pilaf</t>
         </is>
       </c>
-      <c r="J161" t="n">
+      <c r="J161" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="K161" t="n">
+      <c r="K161" s="7" t="n">
         <v>5</v>
       </c>
       <c r="L161" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="M161" t="inlineStr">
+      <c r="M161" s="7" t="inlineStr">
         <is>
           <t>sì</t>
         </is>
       </c>
-      <c r="N161" t="inlineStr">
+      <c r="N161" s="7" t="inlineStr">
         <is>
           <t>Double Buster (onda)</t>
         </is>
@@ -12906,7 +12975,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N162" t="inlineStr">
+      <c r="N162" s="7" t="inlineStr">
         <is>
           <t>Woohoo! (onda)</t>
         </is>
@@ -13118,7 +13187,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q167"/>
+  <autoFilter ref="A1:R167"/>
   <dataValidations count="2">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"sì,-"</formula1>
@@ -13549,7 +13618,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Colonne della scheda di combattimento (spec 037, D-059), tutte facoltative: vuote valgono come la scheda normale. barre: da 3 a 5 (normale 4). potenza e velocità: da 1 a 5, potenza + velocità = 6 (normale 3 e 3). gigante: «sì» se gli impeti non lo colpiscono. mossa 1, mossa 2, mossa finale: nome e tipo, es. «Kamehameha (onda)», «Meteor Smash (impeto)»; «(impeto, giganti)» per un impeto che colpisce anche i giganti, come Penetrate!. Le mosse sono quelle di BT3 (due Blast 2 e la Ultimate), con i nomi inglesi del gioco: l'energia è un'onda, il fisico un impeto (D-057). si trasforma in: il nome della forma successiva, un personaggio di questa lista con un tier.</t>
+          <t>Colonne della scheda di combattimento (spec 037, D-059), tutte facoltative: vuote valgono come la scheda normale. barre: da 3 a 5 (normale 4). potenza e velocità: da 1 a 5, potenza + velocità = 6 (normale 3 e 3). gigante: «sì» se gli impeti non lo colpiscono. mossa 1, mossa 2, mossa finale: nome e tipo, es. «Kamehameha (onda)», «Meteor Smash (impeto)»; «(impeto, giganti)» per un impeto che colpisce anche i giganti, come Penetrate!; «(impeto, risucchio)» o «(onda, risucchio)» per una mossa che restituisce a chi la fa due terzi del danno, come Drain Life (spec 073): chi ha una mossa col risucchio afferra anche l'avversario con i colpi e gli risucchia energia. Androidi e robot non si risucchiano. Le mosse sono quelle di BT3 (due Blast 2 e la Ultimate), con i nomi inglesi del gioco: l'energia è un'onda, il fisico un impeto (D-057). si trasforma in: il nome della forma successiva, un personaggio di questa lista con un tier. cura trasformandosi (spec 073): gli HP che recupera chi si trasforma in questa forma, es. «2500»; vuota, la trasformazione tiene la vita che aveva.</t>
         </is>
       </c>
     </row>

--- a/docs/personaggi-bt3.xlsx
+++ b/docs/personaggi-bt3.xlsx
@@ -12,7 +12,7 @@
     <sheet name="leggimi" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'personaggi'!$A$1:$R$167</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'personaggi'!$A$1:$R$170</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:R167"/>
+  <dimension ref="A1:R170"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="36" customWidth="1" style="7" min="1" max="1"/>
@@ -13147,7 +13147,7 @@
         </is>
       </c>
     </row>
-    <row r="167">
+    <row r="167" s="8">
       <c r="A167" s="12" t="inlineStr">
         <is>
           <t>Chichi (adulta)</t>
@@ -13186,8 +13186,125 @@
         </is>
       </c>
     </row>
+    <row r="168">
+      <c r="A168" s="12" t="inlineStr">
+        <is>
+          <t>Livio</t>
+        </is>
+      </c>
+      <c r="B168" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C168" s="12" t="n"/>
+      <c r="D168" s="12" t="n"/>
+      <c r="E168" s="12" t="inlineStr">
+        <is>
+          <t>Ospiti</t>
+        </is>
+      </c>
+      <c r="F168" s="12" t="inlineStr">
+        <is>
+          <t>Terrestre</t>
+        </is>
+      </c>
+      <c r="G168" s="12" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
+      <c r="H168" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I168" s="12" t="inlineStr">
+        <is>
+          <t>Livio</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="12" t="inlineStr">
+        <is>
+          <t>Maggi</t>
+        </is>
+      </c>
+      <c r="B169" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C169" s="12" t="n"/>
+      <c r="D169" s="12" t="n"/>
+      <c r="E169" s="12" t="inlineStr">
+        <is>
+          <t>Ospiti</t>
+        </is>
+      </c>
+      <c r="F169" s="12" t="inlineStr">
+        <is>
+          <t>Terrestre</t>
+        </is>
+      </c>
+      <c r="G169" s="12" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
+      <c r="H169" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" s="12" t="inlineStr">
+        <is>
+          <t>Maggi</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="12" t="inlineStr">
+        <is>
+          <t>Meliador</t>
+        </is>
+      </c>
+      <c r="B170" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C170" s="12" t="n"/>
+      <c r="D170" s="12" t="n"/>
+      <c r="E170" s="12" t="inlineStr">
+        <is>
+          <t>Ospiti</t>
+        </is>
+      </c>
+      <c r="F170" s="12" t="inlineStr">
+        <is>
+          <t>Terrestre</t>
+        </is>
+      </c>
+      <c r="G170" s="12" t="inlineStr">
+        <is>
+          <t>sì</t>
+        </is>
+      </c>
+      <c r="H170" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I170" s="12" t="inlineStr">
+        <is>
+          <t>Meliador</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R167"/>
+  <autoFilter ref="A1:R170"/>
   <dataValidations count="2">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"sì,-"</formula1>
@@ -13541,7 +13658,7 @@
     <row r="2" ht="15" customHeight="1" s="8">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>Foglio 'personaggi': una riga per personaggio, 166 voci (ogni forma è una voce a sé, spec 002): 161 dal roster più 5 personaggi della storia non arruolabili (Kami, Karin, Bulma, Baba la Veggente, Chichi adulta).</t>
+          <t>Foglio 'personaggi': una riga per personaggio, 169 voci (ogni forma è una voce a sé, spec 002): 161 dal roster più 5 personaggi della storia non arruolabili (Kami, Karin, Bulma, Baba la Veggente, Chichi adulta) e 3 ospiti (Livio, Maggi e Meliador, spec 074).</t>
         </is>
       </c>
     </row>
@@ -13562,14 +13679,14 @@
     <row r="5" ht="15" customHeight="1" s="8">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>negoziante: sì per chi può fare il negoziante (Muten Roshi, Son Gohan (nonno), Kami, Karin, Bulma, Baba la Veggente), - per tutti gli altri. «Randomizza» sceglie i negozianti solo tra questi (spec 022).</t>
+          <t>negoziante: sì per chi può fare il negoziante (Muten Roshi, Son Gohan (nonno), Kami, Karin, Bulma, Baba la Veggente, Livio, Maggi, Meliador), - per tutti gli altri. «Randomizza» sceglie i negozianti solo tra questi (spec 022).</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="8">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>saga: valori usati → Dragon Ball, Saiyan, Freezer, Cell, Majin Bu, Film e speciali, GT, Extra.</t>
+          <t>saga: valori usati → Dragon Ball, Saiyan, Freezer, Cell, Majin Bu, Film e speciali, GT, Extra, Ospiti.</t>
         </is>
       </c>
     </row>

--- a/docs/personaggi-bt3.xlsx
+++ b/docs/personaggi-bt3.xlsx
@@ -9385,7 +9385,7 @@
     <row r="116" ht="15" customHeight="1" s="8">
       <c r="A116" s="12" t="inlineStr">
         <is>
-          <t>Bobbidi</t>
+          <t>Babidi</t>
         </is>
       </c>
       <c r="B116" s="12" t="inlineStr">
@@ -9424,7 +9424,7 @@
       </c>
       <c r="I116" s="12" t="inlineStr">
         <is>
-          <t>Bobbidi</t>
+          <t>Babidi</t>
         </is>
       </c>
       <c r="J116" s="7" t="n">
